--- a/research/traditional_assets/database/data/bulgaria/bulgaria_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_construction_supplies.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09205096276314527</v>
+        <v>0.09199941180038212</v>
       </c>
       <c r="C2">
-        <v>106.5327189530139</v>
+        <v>105.5971891986447</v>
       </c>
       <c r="D2">
-        <v>91.83271895301387</v>
+        <v>91.93518919864469</v>
       </c>
       <c r="E2">
-        <v>-14.1</v>
+        <v>-13.062</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.038</v>
       </c>
       <c r="G2">
         <v>14.7</v>
@@ -1451,28 +1451,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0522114</v>
       </c>
       <c r="N2">
-        <v>8.580000000000002</v>
+        <v>8.527788600000003</v>
       </c>
       <c r="O2">
-        <v>0.8580000000000002</v>
+        <v>0.8527788600000004</v>
       </c>
       <c r="P2">
-        <v>7.722000000000001</v>
+        <v>7.675009740000002</v>
       </c>
       <c r="Q2">
-        <v>15.442</v>
+        <v>15.39500974</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09205096276314527</v>
+        <v>0.09247142606099204</v>
       </c>
       <c r="T2">
-        <v>0.7154876843770529</v>
+        <v>0.7219921178713897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>164.3319275100841</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09199941180038212</v>
+        <v>0.09194786083761898</v>
       </c>
       <c r="C3">
-        <v>105.5971891986447</v>
+        <v>104.6618883796897</v>
       </c>
       <c r="D3">
-        <v>91.93518919864469</v>
+        <v>92.03788837968969</v>
       </c>
       <c r="E3">
-        <v>-13.062</v>
+        <v>-12.024</v>
       </c>
       <c r="F3">
-        <v>1.038</v>
+        <v>2.076</v>
       </c>
       <c r="G3">
         <v>14.7</v>
@@ -1533,28 +1533,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M3">
-        <v>0.0522114</v>
+        <v>0.1044228</v>
       </c>
       <c r="N3">
-        <v>8.527788600000003</v>
+        <v>8.475577200000002</v>
       </c>
       <c r="O3">
-        <v>0.8527788600000004</v>
+        <v>0.8475577200000002</v>
       </c>
       <c r="P3">
-        <v>7.675009740000002</v>
+        <v>7.628019480000002</v>
       </c>
       <c r="Q3">
-        <v>15.39500974</v>
+        <v>15.34801948</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09247142606099204</v>
+        <v>0.09290047024246835</v>
       </c>
       <c r="T3">
-        <v>0.7219921178713897</v>
+        <v>0.7286292949064274</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>164.3319275100841</v>
+        <v>82.16596375504203</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09194786083761898</v>
+        <v>0.09189630987485584</v>
       </c>
       <c r="C4">
-        <v>104.6618883796897</v>
+        <v>103.726817264226</v>
       </c>
       <c r="D4">
-        <v>92.03788837968969</v>
+        <v>92.14081726422603</v>
       </c>
       <c r="E4">
-        <v>-12.024</v>
+        <v>-10.986</v>
       </c>
       <c r="F4">
-        <v>2.076</v>
+        <v>3.114</v>
       </c>
       <c r="G4">
         <v>14.7</v>
@@ -1615,28 +1615,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M4">
-        <v>0.1044228</v>
+        <v>0.1566342</v>
       </c>
       <c r="N4">
-        <v>8.475577200000002</v>
+        <v>8.423365800000003</v>
       </c>
       <c r="O4">
-        <v>0.8475577200000002</v>
+        <v>0.8423365800000003</v>
       </c>
       <c r="P4">
-        <v>7.628019480000002</v>
+        <v>7.581029220000002</v>
       </c>
       <c r="Q4">
-        <v>15.34801948</v>
+        <v>15.30102922</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09290047024246835</v>
+        <v>0.09333836069572767</v>
       </c>
       <c r="T4">
-        <v>0.7286292949064274</v>
+        <v>0.7354033209524966</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>82.16596375504203</v>
+        <v>54.77730917002803</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09189630987485584</v>
+        <v>0.09184475891209269</v>
       </c>
       <c r="C5">
-        <v>103.726817264226</v>
+        <v>102.7919766237706</v>
       </c>
       <c r="D5">
-        <v>92.14081726422603</v>
+        <v>92.24397662377056</v>
       </c>
       <c r="E5">
-        <v>-10.986</v>
+        <v>-9.947999999999997</v>
       </c>
       <c r="F5">
-        <v>3.114</v>
+        <v>4.152</v>
       </c>
       <c r="G5">
         <v>14.7</v>
@@ -1697,28 +1697,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M5">
-        <v>0.1566342</v>
+        <v>0.2088456</v>
       </c>
       <c r="N5">
-        <v>8.423365800000003</v>
+        <v>8.371154400000002</v>
       </c>
       <c r="O5">
-        <v>0.8423365800000003</v>
+        <v>0.8371154400000003</v>
       </c>
       <c r="P5">
-        <v>7.581029220000002</v>
+        <v>7.534038960000002</v>
       </c>
       <c r="Q5">
-        <v>15.30102922</v>
+        <v>15.25403896</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09333836069572767</v>
+        <v>0.09378537386676322</v>
       </c>
       <c r="T5">
-        <v>0.7354033209524966</v>
+        <v>0.7423184725411924</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.77730917002803</v>
+        <v>41.08298187752101</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09184475891209269</v>
+        <v>0.09179320794932955</v>
       </c>
       <c r="C6">
-        <v>102.7919766237706</v>
+        <v>101.8573672332991</v>
       </c>
       <c r="D6">
-        <v>92.24397662377056</v>
+        <v>92.34736723329914</v>
       </c>
       <c r="E6">
-        <v>-9.947999999999997</v>
+        <v>-8.909999999999997</v>
       </c>
       <c r="F6">
-        <v>4.152</v>
+        <v>5.19</v>
       </c>
       <c r="G6">
         <v>14.7</v>
@@ -1779,28 +1779,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M6">
-        <v>0.2088456</v>
+        <v>0.261057</v>
       </c>
       <c r="N6">
-        <v>8.371154400000002</v>
+        <v>8.318943000000003</v>
       </c>
       <c r="O6">
-        <v>0.8371154400000003</v>
+        <v>0.8318943000000003</v>
       </c>
       <c r="P6">
-        <v>7.534038960000002</v>
+        <v>7.487048700000003</v>
       </c>
       <c r="Q6">
-        <v>15.25403896</v>
+        <v>15.2070487</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09378537386676322</v>
+        <v>0.09424179784139952</v>
       </c>
       <c r="T6">
-        <v>0.7423184725411924</v>
+        <v>0.7493792062685974</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.08298187752101</v>
+        <v>32.86638550201681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09179320794932955</v>
+        <v>0.09174165698656639</v>
       </c>
       <c r="C7">
-        <v>101.8573672332991</v>
+        <v>100.9229898712661</v>
       </c>
       <c r="D7">
-        <v>92.34736723329914</v>
+        <v>92.45098987126607</v>
       </c>
       <c r="E7">
-        <v>-8.909999999999997</v>
+        <v>-7.871999999999997</v>
       </c>
       <c r="F7">
-        <v>5.19</v>
+        <v>6.228000000000001</v>
       </c>
       <c r="G7">
         <v>14.7</v>
@@ -1861,28 +1861,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M7">
-        <v>0.261057</v>
+        <v>0.3132684</v>
       </c>
       <c r="N7">
-        <v>8.318943000000003</v>
+        <v>8.266731600000002</v>
       </c>
       <c r="O7">
-        <v>0.8318943000000003</v>
+        <v>0.8266731600000002</v>
       </c>
       <c r="P7">
-        <v>7.487048700000003</v>
+        <v>7.440058440000001</v>
       </c>
       <c r="Q7">
-        <v>15.2070487</v>
+        <v>15.16005844</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09424179784139952</v>
+        <v>0.09470793296443233</v>
       </c>
       <c r="T7">
-        <v>0.7493792062685974</v>
+        <v>0.7565901683731815</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.86638550201681</v>
+        <v>27.38865458501401</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09174165698656639</v>
+        <v>0.09169010602380326</v>
       </c>
       <c r="C8">
-        <v>100.9229898712661</v>
+        <v>99.98884531962341</v>
       </c>
       <c r="D8">
-        <v>92.45098987126607</v>
+        <v>92.55484531962341</v>
       </c>
       <c r="E8">
-        <v>-7.871999999999998</v>
+        <v>-6.833999999999999</v>
       </c>
       <c r="F8">
-        <v>6.228</v>
+        <v>7.265999999999999</v>
       </c>
       <c r="G8">
         <v>14.7</v>
@@ -1943,28 +1943,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M8">
-        <v>0.3132683999999999</v>
+        <v>0.3654797999999999</v>
       </c>
       <c r="N8">
-        <v>8.266731600000002</v>
+        <v>8.214520200000003</v>
       </c>
       <c r="O8">
-        <v>0.8266731600000002</v>
+        <v>0.8214520200000003</v>
       </c>
       <c r="P8">
-        <v>7.440058440000001</v>
+        <v>7.393068180000002</v>
       </c>
       <c r="Q8">
-        <v>15.16005844</v>
+        <v>15.11306818</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09470793296443233</v>
+        <v>0.09518409249871318</v>
       </c>
       <c r="T8">
-        <v>0.7565901683731815</v>
+        <v>0.7639562049316274</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.38865458501401</v>
+        <v>23.47598964429773</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09169010602380326</v>
+        <v>0.09163855506104011</v>
       </c>
       <c r="C9">
-        <v>99.98884531962341</v>
+        <v>99.05493436384104</v>
       </c>
       <c r="D9">
-        <v>92.55484531962341</v>
+        <v>92.65893436384104</v>
       </c>
       <c r="E9">
-        <v>-6.833999999999997</v>
+        <v>-5.795999999999998</v>
       </c>
       <c r="F9">
-        <v>7.266000000000001</v>
+        <v>8.304</v>
       </c>
       <c r="G9">
         <v>14.7</v>
@@ -2025,28 +2025,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M9">
-        <v>0.3654798</v>
+        <v>0.4176912</v>
       </c>
       <c r="N9">
-        <v>8.214520200000003</v>
+        <v>8.162308800000002</v>
       </c>
       <c r="O9">
-        <v>0.8214520200000003</v>
+        <v>0.8162308800000002</v>
       </c>
       <c r="P9">
-        <v>7.393068180000002</v>
+        <v>7.346077920000002</v>
       </c>
       <c r="Q9">
-        <v>15.11306818</v>
+        <v>15.06607792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09518409249871318</v>
+        <v>0.09567060332721751</v>
       </c>
       <c r="T9">
-        <v>0.7639562049316275</v>
+        <v>0.7714823727196048</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.47598964429772</v>
+        <v>20.5414909387605</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09163855506104011</v>
+        <v>0.09158700409827697</v>
       </c>
       <c r="C10">
-        <v>99.05493436384104</v>
+        <v>98.12125779292609</v>
       </c>
       <c r="D10">
-        <v>92.65893436384104</v>
+        <v>92.76325779292608</v>
       </c>
       <c r="E10">
-        <v>-5.795999999999998</v>
+        <v>-4.757999999999999</v>
       </c>
       <c r="F10">
-        <v>8.304</v>
+        <v>9.341999999999999</v>
       </c>
       <c r="G10">
         <v>14.7</v>
@@ -2107,28 +2107,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M10">
-        <v>0.4176912</v>
+        <v>0.4699025999999999</v>
       </c>
       <c r="N10">
-        <v>8.162308800000002</v>
+        <v>8.110097400000003</v>
       </c>
       <c r="O10">
-        <v>0.8162308800000002</v>
+        <v>0.8110097400000003</v>
       </c>
       <c r="P10">
-        <v>7.346077920000002</v>
+        <v>7.299087660000002</v>
       </c>
       <c r="Q10">
-        <v>15.06607792</v>
+        <v>15.01908766</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09567060332721751</v>
+        <v>0.09616780670140326</v>
       </c>
       <c r="T10">
-        <v>0.7714823727196048</v>
+        <v>0.7791739507886367</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.5414909387605</v>
+        <v>18.25910305667601</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09158700409827697</v>
+        <v>0.09153545313551383</v>
       </c>
       <c r="C11">
-        <v>98.12125779292609</v>
+        <v>97.18781639944305</v>
       </c>
       <c r="D11">
-        <v>92.76325779292608</v>
+        <v>92.86781639944304</v>
       </c>
       <c r="E11">
-        <v>-4.757999999999999</v>
+        <v>-3.719999999999999</v>
       </c>
       <c r="F11">
-        <v>9.341999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="G11">
         <v>14.7</v>
@@ -2189,28 +2189,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M11">
-        <v>0.4699025999999999</v>
+        <v>0.522114</v>
       </c>
       <c r="N11">
-        <v>8.110097400000003</v>
+        <v>8.057886000000002</v>
       </c>
       <c r="O11">
-        <v>0.8110097400000003</v>
+        <v>0.8057886000000002</v>
       </c>
       <c r="P11">
-        <v>7.299087660000002</v>
+        <v>7.252097400000001</v>
       </c>
       <c r="Q11">
-        <v>15.01908766</v>
+        <v>14.9720974</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09616780670140326</v>
+        <v>0.09667605903945981</v>
       </c>
       <c r="T11">
-        <v>0.7791739507886367</v>
+        <v>0.7870364528147582</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.25910305667601</v>
+        <v>16.43319275100841</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09153545313551383</v>
+        <v>0.09148390217275068</v>
       </c>
       <c r="C12">
-        <v>97.18781639944305</v>
+        <v>96.25461097953382</v>
       </c>
       <c r="D12">
-        <v>92.86781639944304</v>
+        <v>92.97261097953383</v>
       </c>
       <c r="E12">
-        <v>-3.719999999999997</v>
+        <v>-2.681999999999999</v>
       </c>
       <c r="F12">
-        <v>10.38</v>
+        <v>11.418</v>
       </c>
       <c r="G12">
         <v>14.7</v>
@@ -2271,28 +2271,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M12">
-        <v>0.522114</v>
+        <v>0.5743254</v>
       </c>
       <c r="N12">
-        <v>8.057886000000002</v>
+        <v>8.005674600000003</v>
       </c>
       <c r="O12">
-        <v>0.8057886000000002</v>
+        <v>0.8005674600000003</v>
       </c>
       <c r="P12">
-        <v>7.252097400000001</v>
+        <v>7.205107140000003</v>
       </c>
       <c r="Q12">
-        <v>14.9720974</v>
+        <v>14.92510714</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09667605903945981</v>
+        <v>0.09719573277837154</v>
       </c>
       <c r="T12">
-        <v>0.7870364528147582</v>
+        <v>0.7950756402796688</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.43319275100841</v>
+        <v>14.93926613728037</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09148390217275068</v>
+        <v>0.09143235120998754</v>
       </c>
       <c r="C13">
-        <v>96.25461097953382</v>
+        <v>95.32164233293797</v>
       </c>
       <c r="D13">
-        <v>92.97261097953383</v>
+        <v>93.07764233293797</v>
       </c>
       <c r="E13">
-        <v>-2.681999999999999</v>
+        <v>-1.643999999999998</v>
       </c>
       <c r="F13">
-        <v>11.418</v>
+        <v>12.456</v>
       </c>
       <c r="G13">
         <v>14.7</v>
@@ -2353,28 +2353,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M13">
-        <v>0.5743254</v>
+        <v>0.6265367999999999</v>
       </c>
       <c r="N13">
-        <v>8.005674600000003</v>
+        <v>7.953463200000002</v>
       </c>
       <c r="O13">
-        <v>0.8005674600000003</v>
+        <v>0.7953463200000002</v>
       </c>
       <c r="P13">
-        <v>7.205107140000003</v>
+        <v>7.158116880000001</v>
       </c>
       <c r="Q13">
-        <v>14.92510714</v>
+        <v>14.87811688</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09719573277837154</v>
+        <v>0.09772721728407674</v>
       </c>
       <c r="T13">
-        <v>0.7950756402796688</v>
+        <v>0.8032975365506003</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.93926613728037</v>
+        <v>13.694327292507</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09143235120998754</v>
+        <v>0.09155630024722439</v>
       </c>
       <c r="C14">
-        <v>95.32164233293797</v>
+        <v>94.03150472362279</v>
       </c>
       <c r="D14">
-        <v>93.07764233293797</v>
+        <v>92.82550472362279</v>
       </c>
       <c r="E14">
-        <v>-1.643999999999998</v>
+        <v>-0.6059999999999981</v>
       </c>
       <c r="F14">
-        <v>12.456</v>
+        <v>13.494</v>
       </c>
       <c r="G14">
         <v>14.7</v>
@@ -2435,45 +2435,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M14">
-        <v>0.6265367999999999</v>
+        <v>0.6989892</v>
       </c>
       <c r="N14">
-        <v>7.953463200000002</v>
+        <v>7.881010800000002</v>
       </c>
       <c r="O14">
-        <v>0.7953463200000002</v>
+        <v>0.7881010800000002</v>
       </c>
       <c r="P14">
-        <v>7.158116880000001</v>
+        <v>7.092909720000002</v>
       </c>
       <c r="Q14">
-        <v>14.87811688</v>
+        <v>14.81290972</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09772721728407674</v>
+        <v>0.09827091982439584</v>
       </c>
       <c r="T14">
-        <v>0.8032975365506003</v>
+        <v>0.8117084419312083</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.694327292507</v>
+        <v>12.27486776619725</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09155630024722439</v>
+        <v>0.09151824928446124</v>
       </c>
       <c r="C15">
-        <v>94.03150472362279</v>
+        <v>93.07076270875979</v>
       </c>
       <c r="D15">
-        <v>92.82550472362279</v>
+        <v>92.90276270875978</v>
       </c>
       <c r="E15">
-        <v>-0.6059999999999981</v>
+        <v>0.4320000000000039</v>
       </c>
       <c r="F15">
-        <v>13.494</v>
+        <v>14.532</v>
       </c>
       <c r="G15">
         <v>14.7</v>
@@ -2517,28 +2517,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M15">
-        <v>0.6989892</v>
+        <v>0.7527576</v>
       </c>
       <c r="N15">
-        <v>7.881010800000002</v>
+        <v>7.827242400000002</v>
       </c>
       <c r="O15">
-        <v>0.7881010800000002</v>
+        <v>0.7827242400000003</v>
       </c>
       <c r="P15">
-        <v>7.092909720000002</v>
+        <v>7.044518160000002</v>
       </c>
       <c r="Q15">
-        <v>14.81290972</v>
+        <v>14.76451816</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09827091982439584</v>
+        <v>0.09882726660983865</v>
       </c>
       <c r="T15">
-        <v>0.8117084419312083</v>
+        <v>0.8203149497625281</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.27486776619725</v>
+        <v>11.39809149718316</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09151824928446124</v>
+        <v>0.09148019832169808</v>
       </c>
       <c r="C16">
-        <v>93.07076270875979</v>
+        <v>92.11014940352696</v>
       </c>
       <c r="D16">
-        <v>92.90276270875978</v>
+        <v>92.98014940352697</v>
       </c>
       <c r="E16">
-        <v>0.4320000000000039</v>
+        <v>1.470000000000004</v>
       </c>
       <c r="F16">
-        <v>14.532</v>
+        <v>15.57</v>
       </c>
       <c r="G16">
         <v>14.7</v>
@@ -2599,28 +2599,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M16">
-        <v>0.7527576</v>
+        <v>0.8065260000000001</v>
       </c>
       <c r="N16">
-        <v>7.827242400000002</v>
+        <v>7.773474000000002</v>
       </c>
       <c r="O16">
-        <v>0.7827242400000003</v>
+        <v>0.7773474000000002</v>
       </c>
       <c r="P16">
-        <v>7.044518160000002</v>
+        <v>6.996126600000002</v>
       </c>
       <c r="Q16">
-        <v>14.76451816</v>
+        <v>14.7161266</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09882726660983865</v>
+        <v>0.09939670390788011</v>
       </c>
       <c r="T16">
-        <v>0.8203149497625281</v>
+        <v>0.8291239636604673</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.39809149718316</v>
+        <v>10.63821873070428</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09148019832169808</v>
+        <v>0.09144214735893494</v>
       </c>
       <c r="C17">
-        <v>92.11014940352698</v>
+        <v>91.14966512983234</v>
       </c>
       <c r="D17">
-        <v>92.98014940352697</v>
+        <v>93.05766512983234</v>
       </c>
       <c r="E17">
-        <v>1.470000000000001</v>
+        <v>2.508000000000003</v>
       </c>
       <c r="F17">
-        <v>15.57</v>
+        <v>16.608</v>
       </c>
       <c r="G17">
         <v>14.7</v>
@@ -2681,28 +2681,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M17">
-        <v>0.8065259999999999</v>
+        <v>0.8602944</v>
       </c>
       <c r="N17">
-        <v>7.773474000000002</v>
+        <v>7.719705600000002</v>
       </c>
       <c r="O17">
-        <v>0.7773474000000002</v>
+        <v>0.7719705600000002</v>
       </c>
       <c r="P17">
-        <v>6.996126600000002</v>
+        <v>6.947735040000001</v>
       </c>
       <c r="Q17">
-        <v>14.7161266</v>
+        <v>14.66773504</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09939670390788011</v>
+        <v>0.09997969923682731</v>
       </c>
       <c r="T17">
-        <v>0.8291239636604673</v>
+        <v>0.8381427159845477</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.63821873070428</v>
+        <v>9.973330060035265</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09144214735893494</v>
+        <v>0.09166419639617179</v>
       </c>
       <c r="C18">
-        <v>91.14966512983234</v>
+        <v>89.66113145491303</v>
       </c>
       <c r="D18">
-        <v>93.05766512983234</v>
+        <v>92.60713145491303</v>
       </c>
       <c r="E18">
-        <v>2.508000000000003</v>
+        <v>3.546000000000003</v>
       </c>
       <c r="F18">
-        <v>16.608</v>
+        <v>17.646</v>
       </c>
       <c r="G18">
         <v>14.7</v>
@@ -2763,45 +2763,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M18">
-        <v>0.8602944</v>
+        <v>0.944061</v>
       </c>
       <c r="N18">
-        <v>7.719705600000002</v>
+        <v>7.635939000000002</v>
       </c>
       <c r="O18">
-        <v>0.7719705600000002</v>
+        <v>0.7635939000000003</v>
       </c>
       <c r="P18">
-        <v>6.947735040000001</v>
+        <v>6.872345100000002</v>
       </c>
       <c r="Q18">
-        <v>14.66773504</v>
+        <v>14.5923451</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09997969923682731</v>
+        <v>0.1005767426459901</v>
       </c>
       <c r="T18">
-        <v>0.8381427159845477</v>
+        <v>0.8473787876417386</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.973330060035265</v>
+        <v>9.088395771035984</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09166419639617179</v>
+        <v>0.09164144543340866</v>
       </c>
       <c r="C19">
-        <v>89.66113145491303</v>
+        <v>88.66909207808736</v>
       </c>
       <c r="D19">
-        <v>92.60713145491303</v>
+        <v>92.65309207808735</v>
       </c>
       <c r="E19">
-        <v>3.546000000000003</v>
+        <v>4.584000000000003</v>
       </c>
       <c r="F19">
-        <v>17.646</v>
+        <v>18.684</v>
       </c>
       <c r="G19">
         <v>14.7</v>
@@ -2845,28 +2845,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M19">
-        <v>0.944061</v>
+        <v>0.999594</v>
       </c>
       <c r="N19">
-        <v>7.635939000000002</v>
+        <v>7.580406000000002</v>
       </c>
       <c r="O19">
-        <v>0.7635939000000003</v>
+        <v>0.7580406000000002</v>
       </c>
       <c r="P19">
-        <v>6.872345100000002</v>
+        <v>6.822365400000002</v>
       </c>
       <c r="Q19">
-        <v>14.5923451</v>
+        <v>14.5423654</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1005767426459901</v>
+        <v>0.1011883480895228</v>
       </c>
       <c r="T19">
-        <v>0.8473787876417386</v>
+        <v>0.8568401293393487</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.088395771035984</v>
+        <v>8.583484894867318</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09164144543340866</v>
+        <v>0.09161869447064552</v>
       </c>
       <c r="C20">
-        <v>88.66909207808736</v>
+        <v>87.67709834413469</v>
       </c>
       <c r="D20">
-        <v>92.65309207808735</v>
+        <v>92.69909834413468</v>
       </c>
       <c r="E20">
-        <v>4.584</v>
+        <v>5.622000000000003</v>
       </c>
       <c r="F20">
-        <v>18.684</v>
+        <v>19.722</v>
       </c>
       <c r="G20">
         <v>14.7</v>
@@ -2927,28 +2927,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M20">
-        <v>0.9995939999999999</v>
+        <v>1.055127</v>
       </c>
       <c r="N20">
-        <v>7.580406000000002</v>
+        <v>7.524873000000001</v>
       </c>
       <c r="O20">
-        <v>0.7580406000000002</v>
+        <v>0.7524873000000002</v>
       </c>
       <c r="P20">
-        <v>6.822365400000002</v>
+        <v>6.772385700000001</v>
       </c>
       <c r="Q20">
-        <v>14.5423654</v>
+        <v>14.4923857</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1011883480895228</v>
+        <v>0.1018150549020315</v>
       </c>
       <c r="T20">
-        <v>0.8568401293393487</v>
+        <v>0.8665350844122085</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.583484894867318</v>
+        <v>8.131722531979563</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09161869447064552</v>
+        <v>0.09159594350788237</v>
       </c>
       <c r="C21">
-        <v>87.67709834413469</v>
+        <v>86.6851503210798</v>
       </c>
       <c r="D21">
-        <v>92.69909834413468</v>
+        <v>92.74515032107981</v>
       </c>
       <c r="E21">
-        <v>5.622000000000003</v>
+        <v>6.660000000000004</v>
       </c>
       <c r="F21">
-        <v>19.722</v>
+        <v>20.76</v>
       </c>
       <c r="G21">
         <v>14.7</v>
@@ -3009,28 +3009,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M21">
-        <v>1.055127</v>
+        <v>1.11066</v>
       </c>
       <c r="N21">
-        <v>7.524873000000001</v>
+        <v>7.469340000000002</v>
       </c>
       <c r="O21">
-        <v>0.7524873000000002</v>
+        <v>0.7469340000000002</v>
       </c>
       <c r="P21">
-        <v>6.772385700000001</v>
+        <v>6.722406000000001</v>
       </c>
       <c r="Q21">
-        <v>14.4923857</v>
+        <v>14.442406</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1018150549020315</v>
+        <v>0.102457429384853</v>
       </c>
       <c r="T21">
-        <v>0.8665350844122085</v>
+        <v>0.8764724133618899</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.131722531979563</v>
+        <v>7.725136405380586</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09159594350788237</v>
+        <v>0.09172439254511922</v>
       </c>
       <c r="C22">
-        <v>86.6851503210798</v>
+        <v>85.38774514211255</v>
       </c>
       <c r="D22">
-        <v>92.74515032107981</v>
+        <v>92.48574514211255</v>
       </c>
       <c r="E22">
-        <v>6.660000000000004</v>
+        <v>7.698000000000004</v>
       </c>
       <c r="F22">
-        <v>20.76</v>
+        <v>21.798</v>
       </c>
       <c r="G22">
         <v>14.7</v>
@@ -3091,45 +3091,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M22">
-        <v>1.11066</v>
+        <v>1.1836314</v>
       </c>
       <c r="N22">
-        <v>7.469340000000002</v>
+        <v>7.396368600000002</v>
       </c>
       <c r="O22">
-        <v>0.7469340000000002</v>
+        <v>0.7396368600000002</v>
       </c>
       <c r="P22">
-        <v>6.722406000000001</v>
+        <v>6.656731740000001</v>
       </c>
       <c r="Q22">
-        <v>14.442406</v>
+        <v>14.37673174</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.102457429384853</v>
+        <v>0.1031160665128091</v>
       </c>
       <c r="T22">
-        <v>0.8764724133618899</v>
+        <v>0.8866613202596643</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.725136405380586</v>
+        <v>7.248878324789289</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09172439254511922</v>
+        <v>0.09170884158235607</v>
       </c>
       <c r="C23">
-        <v>85.38774514211255</v>
+        <v>84.38107336406838</v>
       </c>
       <c r="D23">
-        <v>92.48574514211255</v>
+        <v>92.51707336406838</v>
       </c>
       <c r="E23">
-        <v>7.698</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="F23">
-        <v>21.798</v>
+        <v>22.836</v>
       </c>
       <c r="G23">
         <v>14.7</v>
@@ -3173,28 +3173,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M23">
-        <v>1.1836314</v>
+        <v>1.2399948</v>
       </c>
       <c r="N23">
-        <v>7.396368600000002</v>
+        <v>7.340005200000002</v>
       </c>
       <c r="O23">
-        <v>0.7396368600000003</v>
+        <v>0.7340005200000003</v>
       </c>
       <c r="P23">
-        <v>6.656731740000002</v>
+        <v>6.606004680000002</v>
       </c>
       <c r="Q23">
-        <v>14.37673174</v>
+        <v>14.32600468</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1031160665128091</v>
+        <v>0.1037915917722514</v>
       </c>
       <c r="T23">
-        <v>0.8866613202596643</v>
+        <v>0.8971114811804586</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.248878324789291</v>
+        <v>6.919383855480687</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09170884158235607</v>
+        <v>0.09169329061959294</v>
       </c>
       <c r="C24">
-        <v>84.38107336406838</v>
+        <v>83.37442281718918</v>
       </c>
       <c r="D24">
-        <v>92.51707336406838</v>
+        <v>92.54842281718918</v>
       </c>
       <c r="E24">
-        <v>8.736000000000001</v>
+        <v>9.774000000000001</v>
       </c>
       <c r="F24">
-        <v>22.836</v>
+        <v>23.874</v>
       </c>
       <c r="G24">
         <v>14.7</v>
@@ -3255,28 +3255,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M24">
-        <v>1.2399948</v>
+        <v>1.2963582</v>
       </c>
       <c r="N24">
-        <v>7.340005200000002</v>
+        <v>7.283641800000002</v>
       </c>
       <c r="O24">
-        <v>0.7340005200000003</v>
+        <v>0.7283641800000002</v>
       </c>
       <c r="P24">
-        <v>6.606004680000002</v>
+        <v>6.555277620000002</v>
       </c>
       <c r="Q24">
-        <v>14.32600468</v>
+        <v>14.27527762</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1037915917722514</v>
+        <v>0.1044846631423285</v>
       </c>
       <c r="T24">
-        <v>0.8971114811804586</v>
+        <v>0.9078330748524425</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.919383855480687</v>
+        <v>6.618541079155438</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09169329061959294</v>
+        <v>0.09167773965682978</v>
       </c>
       <c r="C25">
-        <v>83.37442281718918</v>
+        <v>82.36779352306495</v>
       </c>
       <c r="D25">
-        <v>92.54842281718918</v>
+        <v>92.57979352306495</v>
       </c>
       <c r="E25">
-        <v>9.774000000000001</v>
+        <v>10.812</v>
       </c>
       <c r="F25">
-        <v>23.874</v>
+        <v>24.912</v>
       </c>
       <c r="G25">
         <v>14.7</v>
@@ -3337,28 +3337,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M25">
-        <v>1.2963582</v>
+        <v>1.3527216</v>
       </c>
       <c r="N25">
-        <v>7.283641800000002</v>
+        <v>7.227278400000001</v>
       </c>
       <c r="O25">
-        <v>0.7283641800000002</v>
+        <v>0.7227278400000001</v>
       </c>
       <c r="P25">
-        <v>6.555277620000002</v>
+        <v>6.504550560000001</v>
       </c>
       <c r="Q25">
-        <v>14.27527762</v>
+        <v>14.22455056</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1044846631423285</v>
+        <v>0.1051959732326708</v>
       </c>
       <c r="T25">
-        <v>0.9078330748524425</v>
+        <v>0.9188368157263206</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.618541079155438</v>
+        <v>6.342768534190627</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09167773965682978</v>
+        <v>0.09188718869406663</v>
       </c>
       <c r="C26">
-        <v>82.36779352306496</v>
+        <v>80.90905298387278</v>
       </c>
       <c r="D26">
-        <v>92.57979352306495</v>
+        <v>92.15905298387278</v>
       </c>
       <c r="E26">
-        <v>10.812</v>
+        <v>11.85</v>
       </c>
       <c r="F26">
-        <v>24.912</v>
+        <v>25.95</v>
       </c>
       <c r="G26">
         <v>14.7</v>
@@ -3419,45 +3419,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M26">
-        <v>1.3527216</v>
+        <v>1.435035</v>
       </c>
       <c r="N26">
-        <v>7.227278400000002</v>
+        <v>7.144965000000002</v>
       </c>
       <c r="O26">
-        <v>0.7227278400000002</v>
+        <v>0.7144965000000002</v>
       </c>
       <c r="P26">
-        <v>6.504550560000002</v>
+        <v>6.430468500000002</v>
       </c>
       <c r="Q26">
-        <v>14.22455056</v>
+        <v>14.1504685</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1051959732326708</v>
+        <v>0.1059262515920888</v>
       </c>
       <c r="T26">
-        <v>0.9188368157263206</v>
+        <v>0.9301339896901688</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.342768534190629</v>
+        <v>5.978948248648988</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09188718869406663</v>
+        <v>0.09188063773130349</v>
       </c>
       <c r="C27">
-        <v>80.90905298387278</v>
+        <v>79.88415459344478</v>
       </c>
       <c r="D27">
-        <v>92.15905298387278</v>
+        <v>92.17215459344477</v>
       </c>
       <c r="E27">
-        <v>11.85</v>
+        <v>12.888</v>
       </c>
       <c r="F27">
-        <v>25.95</v>
+        <v>26.988</v>
       </c>
       <c r="G27">
         <v>14.7</v>
@@ -3501,28 +3501,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M27">
-        <v>1.435035</v>
+        <v>1.4924364</v>
       </c>
       <c r="N27">
-        <v>7.144965000000002</v>
+        <v>7.087563600000002</v>
       </c>
       <c r="O27">
-        <v>0.7144965000000002</v>
+        <v>0.7087563600000002</v>
       </c>
       <c r="P27">
-        <v>6.430468500000002</v>
+        <v>6.378807240000002</v>
       </c>
       <c r="Q27">
-        <v>14.1504685</v>
+        <v>14.09880724</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1059262515920888</v>
+        <v>0.1066762672044642</v>
       </c>
       <c r="T27">
-        <v>0.9301339896901688</v>
+        <v>0.941736492680067</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.978948248648988</v>
+        <v>5.748988700624028</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09188063773130349</v>
+        <v>0.09187408676854035</v>
       </c>
       <c r="C28">
-        <v>79.88415459344478</v>
+        <v>78.85925992867526</v>
       </c>
       <c r="D28">
-        <v>92.17215459344477</v>
+        <v>92.18525992867525</v>
       </c>
       <c r="E28">
-        <v>12.888</v>
+        <v>13.926</v>
       </c>
       <c r="F28">
-        <v>26.988</v>
+        <v>28.026</v>
       </c>
       <c r="G28">
         <v>14.7</v>
@@ -3583,28 +3583,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M28">
-        <v>1.4924364</v>
+        <v>1.5498378</v>
       </c>
       <c r="N28">
-        <v>7.087563600000002</v>
+        <v>7.030162200000002</v>
       </c>
       <c r="O28">
-        <v>0.7087563600000002</v>
+        <v>0.7030162200000003</v>
       </c>
       <c r="P28">
-        <v>6.378807240000002</v>
+        <v>6.327145980000002</v>
       </c>
       <c r="Q28">
-        <v>14.09880724</v>
+        <v>14.04714598</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1066762672044642</v>
+        <v>0.1074468311897813</v>
       </c>
       <c r="T28">
-        <v>0.941736492680067</v>
+        <v>0.9536568724642089</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.748988700624028</v>
+        <v>5.536063193193509</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09187408676854035</v>
+        <v>0.09186753580577721</v>
       </c>
       <c r="C29">
-        <v>78.85925992867526</v>
+        <v>77.83436899115364</v>
       </c>
       <c r="D29">
-        <v>92.18525992867525</v>
+        <v>92.19836899115364</v>
       </c>
       <c r="E29">
-        <v>13.926</v>
+        <v>14.96400000000001</v>
       </c>
       <c r="F29">
-        <v>28.026</v>
+        <v>29.064</v>
       </c>
       <c r="G29">
         <v>14.7</v>
@@ -3665,28 +3665,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M29">
-        <v>1.5498378</v>
+        <v>1.6072392</v>
       </c>
       <c r="N29">
-        <v>7.030162200000002</v>
+        <v>6.972760800000001</v>
       </c>
       <c r="O29">
-        <v>0.7030162200000003</v>
+        <v>0.6972760800000002</v>
       </c>
       <c r="P29">
-        <v>6.327145980000002</v>
+        <v>6.275484720000001</v>
       </c>
       <c r="Q29">
-        <v>14.04714598</v>
+        <v>13.99548472</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1074468311897813</v>
+        <v>0.1082387997302461</v>
       </c>
       <c r="T29">
-        <v>0.9536568724642089</v>
+        <v>0.9659083739090215</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.536063193193509</v>
+        <v>5.338346650579454</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09186753580577721</v>
+        <v>0.09186098484301405</v>
       </c>
       <c r="C30">
-        <v>77.83436899115364</v>
+        <v>76.80948178247027</v>
       </c>
       <c r="D30">
-        <v>92.19836899115364</v>
+        <v>92.21148178247027</v>
       </c>
       <c r="E30">
-        <v>14.96400000000001</v>
+        <v>16.00200000000001</v>
       </c>
       <c r="F30">
-        <v>29.064</v>
+        <v>30.102</v>
       </c>
       <c r="G30">
         <v>14.7</v>
@@ -3747,28 +3747,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M30">
-        <v>1.6072392</v>
+        <v>1.6646406</v>
       </c>
       <c r="N30">
-        <v>6.972760800000001</v>
+        <v>6.915359400000002</v>
       </c>
       <c r="O30">
-        <v>0.6972760800000002</v>
+        <v>0.6915359400000002</v>
       </c>
       <c r="P30">
-        <v>6.275484720000001</v>
+        <v>6.223823460000001</v>
       </c>
       <c r="Q30">
-        <v>13.99548472</v>
+        <v>13.94382346</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1082387997302461</v>
+        <v>0.1090530772436818</v>
       </c>
       <c r="T30">
-        <v>0.9659083739090215</v>
+        <v>0.9785049880705894</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.338346650579454</v>
+        <v>5.154265731593955</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09186098484301405</v>
+        <v>0.0918544338802509</v>
       </c>
       <c r="C31">
-        <v>76.80948178247027</v>
+        <v>75.78459830421632</v>
       </c>
       <c r="D31">
-        <v>92.21148178247027</v>
+        <v>92.22459830421631</v>
       </c>
       <c r="E31">
-        <v>16.002</v>
+        <v>17.04</v>
       </c>
       <c r="F31">
-        <v>30.102</v>
+        <v>31.14</v>
       </c>
       <c r="G31">
         <v>14.7</v>
@@ -3829,28 +3829,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M31">
-        <v>1.6646406</v>
+        <v>1.722042</v>
       </c>
       <c r="N31">
-        <v>6.915359400000002</v>
+        <v>6.857958000000002</v>
       </c>
       <c r="O31">
-        <v>0.6915359400000002</v>
+        <v>0.6857958000000002</v>
       </c>
       <c r="P31">
-        <v>6.223823460000001</v>
+        <v>6.172162200000002</v>
       </c>
       <c r="Q31">
-        <v>13.94382346</v>
+        <v>13.8921622</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1090530772436818</v>
+        <v>0.1098906198289299</v>
       </c>
       <c r="T31">
-        <v>0.9785049880705892</v>
+        <v>0.9914615054939161</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.154265731593957</v>
+        <v>4.982456873874158</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0918544338802509</v>
+        <v>0.09184788291748776</v>
       </c>
       <c r="C32">
-        <v>75.78459830421632</v>
+        <v>74.75971855798389</v>
       </c>
       <c r="D32">
-        <v>92.22459830421631</v>
+        <v>92.23771855798388</v>
       </c>
       <c r="E32">
-        <v>17.04</v>
+        <v>18.078</v>
       </c>
       <c r="F32">
-        <v>31.14</v>
+        <v>32.178</v>
       </c>
       <c r="G32">
         <v>14.7</v>
@@ -3911,28 +3911,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M32">
-        <v>1.722042</v>
+        <v>1.7794434</v>
       </c>
       <c r="N32">
-        <v>6.857958000000002</v>
+        <v>6.800556600000002</v>
       </c>
       <c r="O32">
-        <v>0.6857958000000002</v>
+        <v>0.6800556600000003</v>
       </c>
       <c r="P32">
-        <v>6.172162200000002</v>
+        <v>6.120500940000001</v>
       </c>
       <c r="Q32">
-        <v>13.8921622</v>
+        <v>13.84050094</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1098906198289299</v>
+        <v>0.1107524390108518</v>
       </c>
       <c r="T32">
-        <v>0.9914615054939161</v>
+        <v>1.004793574146905</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.982456873874158</v>
+        <v>4.821732458587895</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09184788291748776</v>
+        <v>0.09184133195472463</v>
       </c>
       <c r="C33">
-        <v>74.75971855798389</v>
+        <v>73.73484254536598</v>
       </c>
       <c r="D33">
-        <v>92.23771855798388</v>
+        <v>92.25084254536598</v>
       </c>
       <c r="E33">
-        <v>18.078</v>
+        <v>19.116</v>
       </c>
       <c r="F33">
-        <v>32.178</v>
+        <v>33.216</v>
       </c>
       <c r="G33">
         <v>14.7</v>
@@ -3993,28 +3993,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M33">
-        <v>1.7794434</v>
+        <v>1.8368448</v>
       </c>
       <c r="N33">
-        <v>6.800556600000002</v>
+        <v>6.743155200000002</v>
       </c>
       <c r="O33">
-        <v>0.6800556600000003</v>
+        <v>0.6743155200000003</v>
       </c>
       <c r="P33">
-        <v>6.120500940000001</v>
+        <v>6.068839680000002</v>
       </c>
       <c r="Q33">
-        <v>13.84050094</v>
+        <v>13.78883968</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1107524390108518</v>
+        <v>0.1116396058157715</v>
       </c>
       <c r="T33">
-        <v>1.004793574146905</v>
+        <v>1.018517762466158</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.821732458587895</v>
+        <v>4.671053319257022</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09184133195472463</v>
+        <v>0.09183478099196148</v>
       </c>
       <c r="C34">
-        <v>73.73484254536598</v>
+        <v>72.70997026795666</v>
       </c>
       <c r="D34">
-        <v>92.25084254536598</v>
+        <v>92.26397026795665</v>
       </c>
       <c r="E34">
-        <v>19.116</v>
+        <v>20.154</v>
       </c>
       <c r="F34">
-        <v>33.216</v>
+        <v>34.254</v>
       </c>
       <c r="G34">
         <v>14.7</v>
@@ -4075,28 +4075,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M34">
-        <v>1.8368448</v>
+        <v>1.8942462</v>
       </c>
       <c r="N34">
-        <v>6.743155200000002</v>
+        <v>6.685753800000002</v>
       </c>
       <c r="O34">
-        <v>0.6743155200000003</v>
+        <v>0.6685753800000003</v>
       </c>
       <c r="P34">
-        <v>6.068839680000002</v>
+        <v>6.017178420000002</v>
       </c>
       <c r="Q34">
-        <v>13.78883968</v>
+        <v>13.73717842</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1116396058157715</v>
+        <v>0.1125532552118828</v>
       </c>
       <c r="T34">
-        <v>1.018517762466158</v>
+        <v>1.032651628048672</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.671053319257022</v>
+        <v>4.529506248976507</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09183478099196148</v>
+        <v>0.09259323002919832</v>
       </c>
       <c r="C35">
-        <v>72.70997026795666</v>
+        <v>70.17650779661804</v>
       </c>
       <c r="D35">
-        <v>92.26397026795665</v>
+        <v>90.76850779661804</v>
       </c>
       <c r="E35">
-        <v>20.154</v>
+        <v>21.192</v>
       </c>
       <c r="F35">
-        <v>34.254</v>
+        <v>35.292</v>
       </c>
       <c r="G35">
         <v>14.7</v>
@@ -4157,45 +4157,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M35">
-        <v>1.8942462</v>
+        <v>2.0398776</v>
       </c>
       <c r="N35">
-        <v>6.685753800000002</v>
+        <v>6.540122400000001</v>
       </c>
       <c r="O35">
-        <v>0.6685753800000003</v>
+        <v>0.6540122400000001</v>
       </c>
       <c r="P35">
-        <v>6.017178420000002</v>
+        <v>5.886110160000001</v>
       </c>
       <c r="Q35">
-        <v>13.73717842</v>
+        <v>13.60611016</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1125532552118828</v>
+        <v>0.1134945909533308</v>
       </c>
       <c r="T35">
-        <v>1.032651628048672</v>
+        <v>1.047213792588232</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.1</v>
       </c>
       <c r="W35">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.529506248976507</v>
+        <v>4.206134721024439</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09259323002919832</v>
+        <v>0.09260917906643518</v>
       </c>
       <c r="C36">
-        <v>70.17650779661804</v>
+        <v>69.10758073616421</v>
       </c>
       <c r="D36">
-        <v>90.76850779661804</v>
+        <v>90.7375807361642</v>
       </c>
       <c r="E36">
-        <v>21.192</v>
+        <v>22.23000000000001</v>
       </c>
       <c r="F36">
-        <v>35.292</v>
+        <v>36.33000000000001</v>
       </c>
       <c r="G36">
         <v>14.7</v>
@@ -4239,28 +4239,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M36">
-        <v>2.0398776</v>
+        <v>2.099874000000001</v>
       </c>
       <c r="N36">
-        <v>6.540122400000001</v>
+        <v>6.480126000000001</v>
       </c>
       <c r="O36">
-        <v>0.6540122400000001</v>
+        <v>0.6480126000000002</v>
       </c>
       <c r="P36">
-        <v>5.886110160000001</v>
+        <v>5.832113400000001</v>
       </c>
       <c r="Q36">
-        <v>13.60611016</v>
+        <v>13.5521134</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1134945909533308</v>
+        <v>0.1144648908714387</v>
       </c>
       <c r="T36">
-        <v>1.047213792588232</v>
+        <v>1.062224023729009</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.206134721024439</v>
+        <v>4.085959443280882</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09260917906643518</v>
+        <v>0.09375912810367204</v>
       </c>
       <c r="C37">
-        <v>69.10758073616421</v>
+        <v>65.89390328466433</v>
       </c>
       <c r="D37">
-        <v>90.7375807361642</v>
+        <v>88.56190328466433</v>
       </c>
       <c r="E37">
-        <v>22.23000000000001</v>
+        <v>23.268</v>
       </c>
       <c r="F37">
-        <v>36.33000000000001</v>
+        <v>37.368</v>
       </c>
       <c r="G37">
         <v>14.7</v>
@@ -4321,45 +4321,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M37">
-        <v>2.099874000000001</v>
+        <v>2.2906584</v>
       </c>
       <c r="N37">
-        <v>6.480126000000001</v>
+        <v>6.289341600000002</v>
       </c>
       <c r="O37">
-        <v>0.6480126000000002</v>
+        <v>0.6289341600000002</v>
       </c>
       <c r="P37">
-        <v>5.832113400000001</v>
+        <v>5.660407440000002</v>
       </c>
       <c r="Q37">
-        <v>13.5521134</v>
+        <v>13.38040744</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1144648908714387</v>
+        <v>0.1154655126619876</v>
       </c>
       <c r="T37">
-        <v>1.062224023729009</v>
+        <v>1.077703324592936</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.085959443280882</v>
+        <v>3.7456479761452</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09375912810367204</v>
+        <v>0.09380657714090888</v>
       </c>
       <c r="C38">
-        <v>65.89390328466433</v>
+        <v>64.76836992367535</v>
       </c>
       <c r="D38">
-        <v>88.56190328466433</v>
+        <v>88.47436992367534</v>
       </c>
       <c r="E38">
-        <v>23.268</v>
+        <v>24.306</v>
       </c>
       <c r="F38">
-        <v>37.36799999999999</v>
+        <v>38.406</v>
       </c>
       <c r="G38">
         <v>14.7</v>
@@ -4403,28 +4403,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M38">
-        <v>2.2906584</v>
+        <v>2.3542878</v>
       </c>
       <c r="N38">
-        <v>6.289341600000002</v>
+        <v>6.225712200000002</v>
       </c>
       <c r="O38">
-        <v>0.6289341600000002</v>
+        <v>0.6225712200000002</v>
       </c>
       <c r="P38">
-        <v>5.660407440000002</v>
+        <v>5.603140980000002</v>
       </c>
       <c r="Q38">
-        <v>13.38040744</v>
+        <v>13.32314098</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1154655126619876</v>
+        <v>0.1164979002236649</v>
       </c>
       <c r="T38">
-        <v>1.077703324592936</v>
+        <v>1.093674031833495</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.7456479761452</v>
+        <v>3.644414247060195</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09380657714090888</v>
+        <v>0.09385402617814576</v>
       </c>
       <c r="C39">
-        <v>64.76836992367535</v>
+        <v>63.64300942535927</v>
       </c>
       <c r="D39">
-        <v>88.47436992367534</v>
+        <v>88.38700942535927</v>
       </c>
       <c r="E39">
-        <v>24.306</v>
+        <v>25.344</v>
       </c>
       <c r="F39">
-        <v>38.406</v>
+        <v>39.444</v>
       </c>
       <c r="G39">
         <v>14.7</v>
@@ -4485,28 +4485,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M39">
-        <v>2.3542878</v>
+        <v>2.4179172</v>
       </c>
       <c r="N39">
-        <v>6.225712200000002</v>
+        <v>6.162082800000002</v>
       </c>
       <c r="O39">
-        <v>0.6225712200000002</v>
+        <v>0.6162082800000003</v>
       </c>
       <c r="P39">
-        <v>5.603140980000002</v>
+        <v>5.545874520000002</v>
       </c>
       <c r="Q39">
-        <v>13.32314098</v>
+        <v>13.26587452</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1164979002236649</v>
+        <v>0.1175635906099125</v>
       </c>
       <c r="T39">
-        <v>1.093674031833495</v>
+        <v>1.110159923178589</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.644414247060195</v>
+        <v>3.548508608979663</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09385402617814576</v>
+        <v>0.0948842752153826</v>
       </c>
       <c r="C40">
-        <v>63.64300942535927</v>
+        <v>60.74981993819367</v>
       </c>
       <c r="D40">
-        <v>88.38700942535927</v>
+        <v>86.53181993819366</v>
       </c>
       <c r="E40">
-        <v>25.344</v>
+        <v>26.382</v>
       </c>
       <c r="F40">
-        <v>39.444</v>
+        <v>40.482</v>
       </c>
       <c r="G40">
         <v>14.7</v>
@@ -4567,45 +4567,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M40">
-        <v>2.4179172</v>
+        <v>2.5948962</v>
       </c>
       <c r="N40">
-        <v>6.162082800000002</v>
+        <v>5.985103800000002</v>
       </c>
       <c r="O40">
-        <v>0.6162082800000003</v>
+        <v>0.5985103800000002</v>
       </c>
       <c r="P40">
-        <v>5.545874520000002</v>
+        <v>5.386593420000001</v>
       </c>
       <c r="Q40">
-        <v>13.26587452</v>
+        <v>13.10659342</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1175635906099125</v>
+        <v>0.1186642216645616</v>
       </c>
       <c r="T40">
-        <v>1.110159923178589</v>
+        <v>1.12718633555139</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.1</v>
       </c>
       <c r="W40">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.548508608979663</v>
+        <v>3.306490641128536</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0948842752153826</v>
+        <v>0.09495692425261947</v>
       </c>
       <c r="C41">
-        <v>60.74981993819367</v>
+        <v>59.58393452826531</v>
       </c>
       <c r="D41">
-        <v>86.53181993819366</v>
+        <v>86.40393452826531</v>
       </c>
       <c r="E41">
-        <v>26.382</v>
+        <v>27.42000000000001</v>
       </c>
       <c r="F41">
-        <v>40.482</v>
+        <v>41.52</v>
       </c>
       <c r="G41">
         <v>14.7</v>
@@ -4649,28 +4649,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M41">
-        <v>2.5948962</v>
+        <v>2.661432</v>
       </c>
       <c r="N41">
-        <v>5.985103800000002</v>
+        <v>5.918568000000001</v>
       </c>
       <c r="O41">
-        <v>0.5985103800000002</v>
+        <v>0.5918568000000002</v>
       </c>
       <c r="P41">
-        <v>5.386593420000001</v>
+        <v>5.326711200000001</v>
       </c>
       <c r="Q41">
-        <v>13.10659342</v>
+        <v>13.0467112</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1186642216645616</v>
+        <v>0.1198015404210324</v>
       </c>
       <c r="T41">
-        <v>1.12718633555139</v>
+        <v>1.144780295003285</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.306490641128536</v>
+        <v>3.223828375100322</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09495692425261947</v>
+        <v>0.09502957328985633</v>
       </c>
       <c r="C42">
-        <v>59.58393452826531</v>
+        <v>58.41842656430234</v>
       </c>
       <c r="D42">
-        <v>86.40393452826531</v>
+        <v>86.27642656430234</v>
       </c>
       <c r="E42">
-        <v>27.42000000000001</v>
+        <v>28.458</v>
       </c>
       <c r="F42">
-        <v>41.52</v>
+        <v>42.558</v>
       </c>
       <c r="G42">
         <v>14.7</v>
@@ -4731,28 +4731,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M42">
-        <v>2.661432</v>
+        <v>2.7279678</v>
       </c>
       <c r="N42">
-        <v>5.918568000000001</v>
+        <v>5.852032200000002</v>
       </c>
       <c r="O42">
-        <v>0.5918568000000002</v>
+        <v>0.5852032200000002</v>
       </c>
       <c r="P42">
-        <v>5.326711200000001</v>
+        <v>5.266828980000001</v>
       </c>
       <c r="Q42">
-        <v>13.0467112</v>
+        <v>12.98682898</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1198015404210324</v>
+        <v>0.1209774123556887</v>
       </c>
       <c r="T42">
-        <v>1.144780295003285</v>
+        <v>1.162970659860328</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.223828375100322</v>
+        <v>3.145198414732022</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09502957328985633</v>
+        <v>0.09510222232709317</v>
       </c>
       <c r="C43">
-        <v>58.41842656430234</v>
+        <v>57.25329437775407</v>
       </c>
       <c r="D43">
-        <v>86.27642656430234</v>
+        <v>86.14929437775407</v>
       </c>
       <c r="E43">
-        <v>28.458</v>
+        <v>29.49600000000001</v>
       </c>
       <c r="F43">
-        <v>42.558</v>
+        <v>43.596</v>
       </c>
       <c r="G43">
         <v>14.7</v>
@@ -4813,28 +4813,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M43">
-        <v>2.7279678</v>
+        <v>2.794503600000001</v>
       </c>
       <c r="N43">
-        <v>5.852032200000002</v>
+        <v>5.785496400000001</v>
       </c>
       <c r="O43">
-        <v>0.5852032200000002</v>
+        <v>0.5785496400000002</v>
       </c>
       <c r="P43">
-        <v>5.266828980000001</v>
+        <v>5.206946760000001</v>
       </c>
       <c r="Q43">
-        <v>12.98682898</v>
+        <v>12.92694676</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1209774123556887</v>
+        <v>0.1221938315984365</v>
       </c>
       <c r="T43">
-        <v>1.162970659860328</v>
+        <v>1.18178827867796</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.145198414732022</v>
+        <v>3.070312738190783</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09510222232709317</v>
+        <v>0.09819347136433003</v>
       </c>
       <c r="C44">
-        <v>57.25329437775408</v>
+        <v>51.13242973127883</v>
       </c>
       <c r="D44">
-        <v>86.14929437775407</v>
+        <v>81.06642973127883</v>
       </c>
       <c r="E44">
-        <v>29.496</v>
+        <v>30.534</v>
       </c>
       <c r="F44">
-        <v>43.596</v>
+        <v>44.634</v>
       </c>
       <c r="G44">
         <v>14.7</v>
@@ -4895,45 +4895,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M44">
-        <v>2.7945036</v>
+        <v>3.2091846</v>
       </c>
       <c r="N44">
-        <v>5.785496400000001</v>
+        <v>5.370815400000001</v>
       </c>
       <c r="O44">
-        <v>0.5785496400000002</v>
+        <v>0.5370815400000002</v>
       </c>
       <c r="P44">
-        <v>5.206946760000001</v>
+        <v>4.833733860000001</v>
       </c>
       <c r="Q44">
-        <v>12.92694676</v>
+        <v>12.55373386</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1221938315984365</v>
+        <v>0.1234529322181228</v>
       </c>
       <c r="T44">
-        <v>1.18178827867796</v>
+        <v>1.201266164822526</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.1</v>
       </c>
       <c r="W44">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.070312738190783</v>
+        <v>2.673576334624066</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09819347136433003</v>
+        <v>0.0983363204015669</v>
       </c>
       <c r="C45">
-        <v>51.13242973127883</v>
+        <v>49.87400581596027</v>
       </c>
       <c r="D45">
-        <v>81.06642973127883</v>
+        <v>80.84600581596027</v>
       </c>
       <c r="E45">
-        <v>30.534</v>
+        <v>31.572</v>
       </c>
       <c r="F45">
-        <v>44.634</v>
+        <v>45.672</v>
       </c>
       <c r="G45">
         <v>14.7</v>
@@ -4977,28 +4977,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M45">
-        <v>3.2091846</v>
+        <v>3.2838168</v>
       </c>
       <c r="N45">
-        <v>5.370815400000001</v>
+        <v>5.296183200000002</v>
       </c>
       <c r="O45">
-        <v>0.5370815400000002</v>
+        <v>0.5296183200000002</v>
       </c>
       <c r="P45">
-        <v>4.833733860000001</v>
+        <v>4.766564880000002</v>
       </c>
       <c r="Q45">
-        <v>12.55373386</v>
+        <v>12.48656488</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1234529322181228</v>
+        <v>0.1247570007170837</v>
       </c>
       <c r="T45">
-        <v>1.201266164822526</v>
+        <v>1.221439689757969</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.673576334624066</v>
+        <v>2.612813236109884</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0983363204015669</v>
+        <v>0.09847916943880373</v>
       </c>
       <c r="C46">
-        <v>49.87400581596027</v>
+        <v>48.6167773387788</v>
       </c>
       <c r="D46">
-        <v>80.84600581596027</v>
+        <v>80.62677733877879</v>
       </c>
       <c r="E46">
-        <v>31.572</v>
+        <v>32.61</v>
       </c>
       <c r="F46">
-        <v>45.672</v>
+        <v>46.71</v>
       </c>
       <c r="G46">
         <v>14.7</v>
@@ -5059,28 +5059,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M46">
-        <v>3.2838168</v>
+        <v>3.358449</v>
       </c>
       <c r="N46">
-        <v>5.296183200000002</v>
+        <v>5.221551000000002</v>
       </c>
       <c r="O46">
-        <v>0.5296183200000002</v>
+        <v>0.5221551000000002</v>
       </c>
       <c r="P46">
-        <v>4.766564880000002</v>
+        <v>4.699395900000002</v>
       </c>
       <c r="Q46">
-        <v>12.48656488</v>
+        <v>12.4193959</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1247570007170837</v>
+        <v>0.126108489888734</v>
       </c>
       <c r="T46">
-        <v>1.221439689757969</v>
+        <v>1.242346797418337</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.612813236109884</v>
+        <v>2.554750719751886</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09847916943880373</v>
+        <v>0.1002366184760406</v>
       </c>
       <c r="C47">
-        <v>48.6167773387788</v>
+        <v>44.97579691537293</v>
       </c>
       <c r="D47">
-        <v>80.62677733877879</v>
+        <v>78.02379691537293</v>
       </c>
       <c r="E47">
-        <v>32.61</v>
+        <v>33.648</v>
       </c>
       <c r="F47">
-        <v>46.71</v>
+        <v>47.748</v>
       </c>
       <c r="G47">
         <v>14.7</v>
@@ -5141,45 +5141,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M47">
-        <v>3.358449</v>
+        <v>3.6192984</v>
       </c>
       <c r="N47">
-        <v>5.221551000000002</v>
+        <v>4.960701600000002</v>
       </c>
       <c r="O47">
-        <v>0.5221551000000002</v>
+        <v>0.4960701600000002</v>
       </c>
       <c r="P47">
-        <v>4.699395900000002</v>
+        <v>4.464631440000002</v>
       </c>
       <c r="Q47">
-        <v>12.4193959</v>
+        <v>12.18463144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.126108489888734</v>
+        <v>0.12751003421489</v>
       </c>
       <c r="T47">
-        <v>1.242346797418337</v>
+        <v>1.26402824239946</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.1</v>
       </c>
       <c r="W47">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.554750719751886</v>
+        <v>2.370625201834699</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1002366184760406</v>
+        <v>0.1004145675132775</v>
       </c>
       <c r="C48">
-        <v>44.97579691537293</v>
+        <v>43.68357427524528</v>
       </c>
       <c r="D48">
-        <v>78.02379691537293</v>
+        <v>77.76957427524528</v>
       </c>
       <c r="E48">
-        <v>33.648</v>
+        <v>34.68600000000001</v>
       </c>
       <c r="F48">
-        <v>47.748</v>
+        <v>48.786</v>
       </c>
       <c r="G48">
         <v>14.7</v>
@@ -5223,28 +5223,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M48">
-        <v>3.6192984</v>
+        <v>3.6979788</v>
       </c>
       <c r="N48">
-        <v>4.960701600000002</v>
+        <v>4.882021200000001</v>
       </c>
       <c r="O48">
-        <v>0.4960701600000002</v>
+        <v>0.4882021200000002</v>
       </c>
       <c r="P48">
-        <v>4.464631440000002</v>
+        <v>4.393819080000001</v>
       </c>
       <c r="Q48">
-        <v>12.18463144</v>
+        <v>12.11381908</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.12751003421489</v>
+        <v>0.1289644670061839</v>
       </c>
       <c r="T48">
-        <v>1.26402824239946</v>
+        <v>1.28652785511572</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.370625201834699</v>
+        <v>2.320186367753109</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1004145675132775</v>
+        <v>0.1005925165505143</v>
       </c>
       <c r="C49">
-        <v>43.68357427524528</v>
+        <v>42.39300290711251</v>
       </c>
       <c r="D49">
-        <v>77.76957427524528</v>
+        <v>77.51700290711251</v>
       </c>
       <c r="E49">
-        <v>34.68600000000001</v>
+        <v>35.724</v>
       </c>
       <c r="F49">
-        <v>48.786</v>
+        <v>49.82400000000001</v>
       </c>
       <c r="G49">
         <v>14.7</v>
@@ -5305,28 +5305,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M49">
-        <v>3.6979788</v>
+        <v>3.776659200000001</v>
       </c>
       <c r="N49">
-        <v>4.882021200000001</v>
+        <v>4.803340800000001</v>
       </c>
       <c r="O49">
-        <v>0.4882021200000002</v>
+        <v>0.4803340800000001</v>
       </c>
       <c r="P49">
-        <v>4.393819080000001</v>
+        <v>4.32300672</v>
       </c>
       <c r="Q49">
-        <v>12.11381908</v>
+        <v>12.04300672</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1289644670061839</v>
+        <v>0.1304748395202198</v>
       </c>
       <c r="T49">
-        <v>1.28652785511572</v>
+        <v>1.309892837551835</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.320186367753109</v>
+        <v>2.271849151758253</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1005925165505143</v>
+        <v>0.1007704655877512</v>
       </c>
       <c r="C50">
-        <v>42.39300290711256</v>
+        <v>41.1040667746036</v>
       </c>
       <c r="D50">
-        <v>77.51700290711256</v>
+        <v>77.26606677460359</v>
       </c>
       <c r="E50">
-        <v>35.724</v>
+        <v>36.762</v>
       </c>
       <c r="F50">
-        <v>49.824</v>
+        <v>50.86199999999999</v>
       </c>
       <c r="G50">
         <v>14.7</v>
@@ -5387,28 +5387,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M50">
-        <v>3.7766592</v>
+        <v>3.8553396</v>
       </c>
       <c r="N50">
-        <v>4.803340800000002</v>
+        <v>4.724660400000002</v>
       </c>
       <c r="O50">
-        <v>0.4803340800000002</v>
+        <v>0.4724660400000003</v>
       </c>
       <c r="P50">
-        <v>4.323006720000001</v>
+        <v>4.252194360000002</v>
       </c>
       <c r="Q50">
-        <v>12.04300672</v>
+        <v>11.97219436</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1304748395202198</v>
+        <v>0.1320444423289238</v>
       </c>
       <c r="T50">
-        <v>1.309892837551835</v>
+        <v>1.334174093808975</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.271849151758253</v>
+        <v>2.225484883355024</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1007704655877512</v>
+        <v>0.100948414624988</v>
       </c>
       <c r="C51">
-        <v>41.1040667746036</v>
+        <v>39.8167500483275</v>
       </c>
       <c r="D51">
-        <v>77.26606677460359</v>
+        <v>77.01675004832749</v>
       </c>
       <c r="E51">
-        <v>36.762</v>
+        <v>37.8</v>
       </c>
       <c r="F51">
-        <v>50.86199999999999</v>
+        <v>51.9</v>
       </c>
       <c r="G51">
         <v>14.7</v>
@@ -5469,28 +5469,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M51">
-        <v>3.8553396</v>
+        <v>3.93402</v>
       </c>
       <c r="N51">
-        <v>4.724660400000002</v>
+        <v>4.645980000000002</v>
       </c>
       <c r="O51">
-        <v>0.4724660400000003</v>
+        <v>0.4645980000000002</v>
       </c>
       <c r="P51">
-        <v>4.252194360000002</v>
+        <v>4.181382000000001</v>
       </c>
       <c r="Q51">
-        <v>11.97219436</v>
+        <v>11.901382</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1320444423289238</v>
+        <v>0.133676829249976</v>
       </c>
       <c r="T51">
-        <v>1.334174093808975</v>
+        <v>1.3594266003164</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.225484883355024</v>
+        <v>2.180975185687922</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.100948414624988</v>
+        <v>0.1011263636622249</v>
       </c>
       <c r="C52">
-        <v>39.8167500483275</v>
+        <v>38.53103710254486</v>
       </c>
       <c r="D52">
-        <v>77.01675004832749</v>
+        <v>76.76903710254486</v>
       </c>
       <c r="E52">
-        <v>37.8</v>
+        <v>38.83800000000001</v>
       </c>
       <c r="F52">
-        <v>51.9</v>
+        <v>52.938</v>
       </c>
       <c r="G52">
         <v>14.7</v>
@@ -5551,28 +5551,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M52">
-        <v>3.93402</v>
+        <v>4.012700400000001</v>
       </c>
       <c r="N52">
-        <v>4.645980000000002</v>
+        <v>4.567299600000001</v>
       </c>
       <c r="O52">
-        <v>0.4645980000000002</v>
+        <v>0.4567299600000001</v>
       </c>
       <c r="P52">
-        <v>4.181382000000001</v>
+        <v>4.110569640000001</v>
       </c>
       <c r="Q52">
-        <v>11.901382</v>
+        <v>11.83056964</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.133676829249976</v>
+        <v>0.1353758442086222</v>
       </c>
       <c r="T52">
-        <v>1.3594266003164</v>
+        <v>1.385709821375149</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.180975185687922</v>
+        <v>2.138210966360708</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1011263636622249</v>
+        <v>0.1013043126994617</v>
       </c>
       <c r="C53">
-        <v>38.53103710254486</v>
+        <v>37.24691251190325</v>
       </c>
       <c r="D53">
-        <v>76.76903710254486</v>
+        <v>76.52291251190324</v>
       </c>
       <c r="E53">
-        <v>38.83800000000001</v>
+        <v>39.876</v>
       </c>
       <c r="F53">
-        <v>52.938</v>
+        <v>53.976</v>
       </c>
       <c r="G53">
         <v>14.7</v>
@@ -5633,28 +5633,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M53">
-        <v>4.012700400000001</v>
+        <v>4.0913808</v>
       </c>
       <c r="N53">
-        <v>4.567299600000001</v>
+        <v>4.488619200000001</v>
       </c>
       <c r="O53">
-        <v>0.4567299600000001</v>
+        <v>0.4488619200000001</v>
       </c>
       <c r="P53">
-        <v>4.110569640000001</v>
+        <v>4.039757280000002</v>
       </c>
       <c r="Q53">
-        <v>11.83056964</v>
+        <v>11.75975728</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1353758442086222</v>
+        <v>0.1371456514572119</v>
       </c>
       <c r="T53">
-        <v>1.385709821375149</v>
+        <v>1.413088176644679</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.138210966360708</v>
+        <v>2.097091524699926</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1013043126994617</v>
+        <v>0.1014822617366986</v>
       </c>
       <c r="C54">
-        <v>37.24691251190325</v>
+        <v>35.9643610482353</v>
       </c>
       <c r="D54">
-        <v>76.52291251190324</v>
+        <v>76.2783610482353</v>
       </c>
       <c r="E54">
-        <v>39.876</v>
+        <v>40.914</v>
       </c>
       <c r="F54">
-        <v>53.976</v>
+        <v>55.014</v>
       </c>
       <c r="G54">
         <v>14.7</v>
@@ -5715,28 +5715,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M54">
-        <v>4.0913808</v>
+        <v>4.1700612</v>
       </c>
       <c r="N54">
-        <v>4.488619200000001</v>
+        <v>4.409938800000002</v>
       </c>
       <c r="O54">
-        <v>0.4488619200000001</v>
+        <v>0.4409938800000002</v>
       </c>
       <c r="P54">
-        <v>4.039757280000002</v>
+        <v>3.968944920000002</v>
       </c>
       <c r="Q54">
-        <v>11.75975728</v>
+        <v>11.68894492</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1371456514572119</v>
+        <v>0.1389907696525501</v>
       </c>
       <c r="T54">
-        <v>1.413088176644679</v>
+        <v>1.441631568308658</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.097091524699926</v>
+        <v>2.057523760082946</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1014822617366986</v>
+        <v>0.1016602107739354</v>
       </c>
       <c r="C55">
-        <v>35.9643610482353</v>
+        <v>34.68336767741767</v>
       </c>
       <c r="D55">
-        <v>76.2783610482353</v>
+        <v>76.03536767741767</v>
       </c>
       <c r="E55">
-        <v>40.914</v>
+        <v>41.952</v>
       </c>
       <c r="F55">
-        <v>55.014</v>
+        <v>56.052</v>
       </c>
       <c r="G55">
         <v>14.7</v>
@@ -5797,28 +5797,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M55">
-        <v>4.1700612</v>
+        <v>4.248741600000001</v>
       </c>
       <c r="N55">
-        <v>4.409938800000002</v>
+        <v>4.331258400000001</v>
       </c>
       <c r="O55">
-        <v>0.4409938800000002</v>
+        <v>0.4331258400000002</v>
       </c>
       <c r="P55">
-        <v>3.968944920000002</v>
+        <v>3.898132560000001</v>
       </c>
       <c r="Q55">
-        <v>11.68894492</v>
+        <v>11.61813256</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1389907696525501</v>
+        <v>0.1409161103781205</v>
       </c>
       <c r="T55">
-        <v>1.441631568308658</v>
+        <v>1.471415977001505</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.057523760082946</v>
+        <v>2.019421468229558</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1016602107739354</v>
+        <v>0.1088671598111723</v>
       </c>
       <c r="C56">
-        <v>34.68336767741767</v>
+        <v>24.95648710122848</v>
       </c>
       <c r="D56">
-        <v>76.03536767741767</v>
+        <v>67.34648710122848</v>
       </c>
       <c r="E56">
-        <v>41.952</v>
+        <v>42.99000000000001</v>
       </c>
       <c r="F56">
-        <v>56.052</v>
+        <v>57.09</v>
       </c>
       <c r="G56">
         <v>14.7</v>
@@ -5879,45 +5879,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M56">
-        <v>4.248741600000001</v>
+        <v>5.138100000000001</v>
       </c>
       <c r="N56">
-        <v>4.331258400000001</v>
+        <v>3.441900000000001</v>
       </c>
       <c r="O56">
-        <v>0.4331258400000002</v>
+        <v>0.3441900000000002</v>
       </c>
       <c r="P56">
-        <v>3.898132560000001</v>
+        <v>3.097710000000001</v>
       </c>
       <c r="Q56">
-        <v>11.61813256</v>
+        <v>10.81771</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1409161103781205</v>
+        <v>0.1429270218026051</v>
       </c>
       <c r="T56">
-        <v>1.471415977001505</v>
+        <v>1.502524137191811</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.1</v>
       </c>
       <c r="W56">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.019421468229558</v>
+        <v>1.669877970456005</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1088671598111723</v>
+        <v>0.1091729088484091</v>
       </c>
       <c r="C57">
-        <v>24.95648710122848</v>
+        <v>23.59356713200724</v>
       </c>
       <c r="D57">
-        <v>67.34648710122848</v>
+        <v>67.02156713200725</v>
       </c>
       <c r="E57">
-        <v>42.99000000000001</v>
+        <v>44.02800000000001</v>
       </c>
       <c r="F57">
-        <v>57.09</v>
+        <v>58.12800000000001</v>
       </c>
       <c r="G57">
         <v>14.7</v>
@@ -5961,28 +5961,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M57">
-        <v>5.138100000000001</v>
+        <v>5.231520000000001</v>
       </c>
       <c r="N57">
-        <v>3.441900000000001</v>
+        <v>3.348480000000001</v>
       </c>
       <c r="O57">
-        <v>0.3441900000000002</v>
+        <v>0.3348480000000001</v>
       </c>
       <c r="P57">
-        <v>3.097710000000001</v>
+        <v>3.013632000000001</v>
       </c>
       <c r="Q57">
-        <v>10.81771</v>
+        <v>10.733632</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1429270218026051</v>
+        <v>0.1450293382918389</v>
       </c>
       <c r="T57">
-        <v>1.502524137191811</v>
+        <v>1.535046304663495</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.669877970456005</v>
+        <v>1.640058720983577</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1091729088484091</v>
+        <v>0.109478657885646</v>
       </c>
       <c r="C58">
-        <v>23.59356713200724</v>
+        <v>22.23376732803656</v>
       </c>
       <c r="D58">
-        <v>67.02156713200725</v>
+        <v>66.69976732803656</v>
       </c>
       <c r="E58">
-        <v>44.02800000000001</v>
+        <v>45.066</v>
       </c>
       <c r="F58">
-        <v>58.12800000000001</v>
+        <v>59.166</v>
       </c>
       <c r="G58">
         <v>14.7</v>
@@ -6043,28 +6043,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M58">
-        <v>5.231520000000001</v>
+        <v>5.32494</v>
       </c>
       <c r="N58">
-        <v>3.348480000000001</v>
+        <v>3.255060000000002</v>
       </c>
       <c r="O58">
-        <v>0.3348480000000001</v>
+        <v>0.3255060000000002</v>
       </c>
       <c r="P58">
-        <v>3.013632000000001</v>
+        <v>2.929554000000002</v>
       </c>
       <c r="Q58">
-        <v>10.733632</v>
+        <v>10.649554</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1450293382918389</v>
+        <v>0.1472294369433628</v>
       </c>
       <c r="T58">
-        <v>1.535046304663495</v>
+        <v>1.569081131087351</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.640058720983577</v>
+        <v>1.611285760966321</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.109478657885646</v>
+        <v>0.1097844069228829</v>
       </c>
       <c r="C59">
-        <v>22.23376732803656</v>
+        <v>20.87704296025352</v>
       </c>
       <c r="D59">
-        <v>66.69976732803656</v>
+        <v>66.38104296025352</v>
       </c>
       <c r="E59">
-        <v>45.066</v>
+        <v>46.10400000000001</v>
       </c>
       <c r="F59">
-        <v>59.166</v>
+        <v>60.20400000000001</v>
       </c>
       <c r="G59">
         <v>14.7</v>
@@ -6125,28 +6125,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M59">
-        <v>5.32494</v>
+        <v>5.418360000000001</v>
       </c>
       <c r="N59">
-        <v>3.255060000000002</v>
+        <v>3.161640000000001</v>
       </c>
       <c r="O59">
-        <v>0.3255060000000002</v>
+        <v>0.3161640000000001</v>
       </c>
       <c r="P59">
-        <v>2.929554000000002</v>
+        <v>2.845476000000001</v>
       </c>
       <c r="Q59">
-        <v>10.649554</v>
+        <v>10.565476</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1472294369433628</v>
+        <v>0.1495343021973401</v>
       </c>
       <c r="T59">
-        <v>1.569081131087351</v>
+        <v>1.60473666353139</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.611285760966321</v>
+        <v>1.583504971984143</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1097844069228829</v>
+        <v>0.1100901559601197</v>
       </c>
       <c r="C60">
-        <v>20.87704296025353</v>
+        <v>19.52335015047927</v>
       </c>
       <c r="D60">
-        <v>66.38104296025352</v>
+        <v>66.06535015047926</v>
       </c>
       <c r="E60">
-        <v>46.104</v>
+        <v>47.142</v>
       </c>
       <c r="F60">
-        <v>60.20399999999999</v>
+        <v>61.242</v>
       </c>
       <c r="G60">
         <v>14.7</v>
@@ -6207,28 +6207,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M60">
-        <v>5.418359999999999</v>
+        <v>5.51178</v>
       </c>
       <c r="N60">
-        <v>3.161640000000003</v>
+        <v>3.068220000000002</v>
       </c>
       <c r="O60">
-        <v>0.3161640000000003</v>
+        <v>0.3068220000000002</v>
       </c>
       <c r="P60">
-        <v>2.845476000000002</v>
+        <v>2.761398000000002</v>
       </c>
       <c r="Q60">
-        <v>10.565476</v>
+        <v>10.481398</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1495343021973401</v>
+        <v>0.151951599902731</v>
       </c>
       <c r="T60">
-        <v>1.60473666353139</v>
+        <v>1.642131490240992</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.583504971984143</v>
+        <v>1.556665904662378</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1100901559601197</v>
+        <v>0.1103959049973565</v>
       </c>
       <c r="C61">
-        <v>19.52335015047927</v>
+        <v>18.17264585128181</v>
       </c>
       <c r="D61">
-        <v>66.06535015047926</v>
+        <v>65.7526458512818</v>
       </c>
       <c r="E61">
-        <v>47.142</v>
+        <v>48.17999999999999</v>
       </c>
       <c r="F61">
-        <v>61.242</v>
+        <v>62.27999999999999</v>
       </c>
       <c r="G61">
         <v>14.7</v>
@@ -6289,28 +6289,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M61">
-        <v>5.51178</v>
+        <v>5.605199999999999</v>
       </c>
       <c r="N61">
-        <v>3.068220000000002</v>
+        <v>2.974800000000003</v>
       </c>
       <c r="O61">
-        <v>0.3068220000000002</v>
+        <v>0.2974800000000003</v>
       </c>
       <c r="P61">
-        <v>2.761398000000002</v>
+        <v>2.677320000000003</v>
       </c>
       <c r="Q61">
-        <v>10.481398</v>
+        <v>10.39732</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.151951599902731</v>
+        <v>0.1544897624933914</v>
       </c>
       <c r="T61">
-        <v>1.642131490240992</v>
+        <v>1.681396058286074</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.556665904662378</v>
+        <v>1.530721472918005</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1103959049973565</v>
+        <v>0.1107016540345934</v>
       </c>
       <c r="C62">
-        <v>18.17264585128181</v>
+        <v>16.82488782640787</v>
       </c>
       <c r="D62">
-        <v>65.7526458512818</v>
+        <v>65.44288782640787</v>
       </c>
       <c r="E62">
-        <v>48.17999999999999</v>
+        <v>49.218</v>
       </c>
       <c r="F62">
-        <v>62.27999999999999</v>
+        <v>63.318</v>
       </c>
       <c r="G62">
         <v>14.7</v>
@@ -6371,28 +6371,28 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M62">
-        <v>5.605199999999999</v>
+        <v>5.69862</v>
       </c>
       <c r="N62">
-        <v>2.974800000000003</v>
+        <v>2.881380000000002</v>
       </c>
       <c r="O62">
-        <v>0.2974800000000003</v>
+        <v>0.2881380000000002</v>
       </c>
       <c r="P62">
-        <v>2.677320000000003</v>
+        <v>2.593242000000002</v>
       </c>
       <c r="Q62">
-        <v>10.39732</v>
+        <v>10.313242</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1544897624933914</v>
+        <v>0.1571580872681883</v>
       </c>
       <c r="T62">
-        <v>1.681396058286074</v>
+        <v>1.722674193923212</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.530721472918005</v>
+        <v>1.505627678280005</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1107016540345934</v>
+        <v>0.143800804915919</v>
       </c>
       <c r="C63">
-        <v>16.82488782640787</v>
+        <v>-6.316032860155602</v>
       </c>
       <c r="D63">
-        <v>65.44288782640787</v>
+        <v>43.33996713984439</v>
       </c>
       <c r="E63">
-        <v>49.218</v>
+        <v>50.256</v>
       </c>
       <c r="F63">
-        <v>63.318</v>
+        <v>64.35599999999999</v>
       </c>
       <c r="G63">
         <v>14.7</v>
@@ -6453,45 +6453,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M63">
-        <v>5.69862</v>
+        <v>9.4474608</v>
       </c>
       <c r="N63">
-        <v>2.881380000000002</v>
+        <v>-0.8674607999999981</v>
       </c>
       <c r="O63">
-        <v>0.2881380000000002</v>
+        <v>-0.08674607999999982</v>
       </c>
       <c r="P63">
-        <v>2.593242000000002</v>
+        <v>-0.7807147199999983</v>
       </c>
       <c r="Q63">
-        <v>10.313242</v>
+        <v>6.939285280000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1571580872681883</v>
+        <v>0.1606597391307269</v>
       </c>
       <c r="T63">
-        <v>1.722674193923212</v>
+        <v>1.776843634577943</v>
       </c>
       <c r="U63">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1</v>
+        <v>0.09081805346046001</v>
       </c>
       <c r="W63">
-        <v>0.081</v>
+        <v>0.1334679097520045</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.505627678280005</v>
+        <v>0.9081805346046</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.143800804915919</v>
+        <v>0.144810804915919</v>
       </c>
       <c r="C64">
-        <v>-6.316032860155602</v>
+        <v>-7.796139828666938</v>
       </c>
       <c r="D64">
-        <v>43.33996713984439</v>
+        <v>42.89786017133306</v>
       </c>
       <c r="E64">
-        <v>50.256</v>
+        <v>51.29400000000001</v>
       </c>
       <c r="F64">
-        <v>64.35599999999999</v>
+        <v>65.39400000000001</v>
       </c>
       <c r="G64">
         <v>14.7</v>
@@ -6535,37 +6535,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M64">
-        <v>9.4474608</v>
+        <v>9.599839200000002</v>
       </c>
       <c r="N64">
-        <v>-0.8674607999999981</v>
+        <v>-1.0198392</v>
       </c>
       <c r="O64">
-        <v>-0.08674607999999982</v>
+        <v>-0.10198392</v>
       </c>
       <c r="P64">
-        <v>-0.7807147199999983</v>
+        <v>-0.9178552799999998</v>
       </c>
       <c r="Q64">
-        <v>6.939285280000002</v>
+        <v>6.80214472</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1606597391307269</v>
+        <v>0.1637640564045303</v>
       </c>
       <c r="T64">
-        <v>1.776843634577943</v>
+        <v>1.824866435512482</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.09081805346046001</v>
+        <v>0.08937649705632571</v>
       </c>
       <c r="W64">
-        <v>0.1334679097520045</v>
+        <v>0.1336795302321314</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9081805346046</v>
+        <v>0.893764970563257</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.144810804915919</v>
+        <v>0.145820804915919</v>
       </c>
       <c r="C65">
-        <v>-7.796139828666938</v>
+        <v>-9.267318094023508</v>
       </c>
       <c r="D65">
-        <v>42.89786017133306</v>
+        <v>42.46468190597649</v>
       </c>
       <c r="E65">
-        <v>51.29400000000001</v>
+        <v>52.33200000000001</v>
       </c>
       <c r="F65">
-        <v>65.39400000000001</v>
+        <v>66.432</v>
       </c>
       <c r="G65">
         <v>14.7</v>
@@ -6617,37 +6617,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M65">
-        <v>9.599839200000002</v>
+        <v>9.752217600000002</v>
       </c>
       <c r="N65">
-        <v>-1.0198392</v>
+        <v>-1.1722176</v>
       </c>
       <c r="O65">
-        <v>-0.10198392</v>
+        <v>-0.11722176</v>
       </c>
       <c r="P65">
-        <v>-0.9178552799999998</v>
+        <v>-1.05499584</v>
       </c>
       <c r="Q65">
-        <v>6.80214472</v>
+        <v>6.665004160000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1637640564045303</v>
+        <v>0.1670408357491006</v>
       </c>
       <c r="T65">
-        <v>1.824866435512482</v>
+        <v>1.875557169832273</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.08937649705632571</v>
+        <v>0.08797998928982061</v>
       </c>
       <c r="W65">
-        <v>0.1336795302321314</v>
+        <v>0.1338845375722544</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.893764970563257</v>
+        <v>0.879799892898206</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.145820804915919</v>
+        <v>0.146830804915919</v>
       </c>
       <c r="C66">
-        <v>-9.267318094023508</v>
+        <v>-10.7298354356475</v>
       </c>
       <c r="D66">
-        <v>42.46468190597649</v>
+        <v>42.0401645643525</v>
       </c>
       <c r="E66">
-        <v>52.33200000000001</v>
+        <v>53.37</v>
       </c>
       <c r="F66">
-        <v>66.432</v>
+        <v>67.47</v>
       </c>
       <c r="G66">
         <v>14.7</v>
@@ -6699,37 +6699,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M66">
-        <v>9.752217600000002</v>
+        <v>9.904596000000002</v>
       </c>
       <c r="N66">
-        <v>-1.1722176</v>
+        <v>-1.324596</v>
       </c>
       <c r="O66">
-        <v>-0.11722176</v>
+        <v>-0.1324596</v>
       </c>
       <c r="P66">
-        <v>-1.05499584</v>
+        <v>-1.1921364</v>
       </c>
       <c r="Q66">
-        <v>6.665004160000001</v>
+        <v>6.5278636</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1670408357491006</v>
+        <v>0.1705048596276463</v>
       </c>
       <c r="T66">
-        <v>1.875557169832273</v>
+        <v>1.929144517541767</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.08797998928982061</v>
+        <v>0.08662645099305415</v>
       </c>
       <c r="W66">
-        <v>0.1338845375722544</v>
+        <v>0.1340832369942197</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.879799892898206</v>
+        <v>0.8662645099305414</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.146830804915919</v>
+        <v>0.147840804915919</v>
       </c>
       <c r="C67">
-        <v>-10.7298354356475</v>
+        <v>-12.18394903103693</v>
       </c>
       <c r="D67">
-        <v>42.0401645643525</v>
+        <v>41.62405096896306</v>
       </c>
       <c r="E67">
-        <v>53.37</v>
+        <v>54.408</v>
       </c>
       <c r="F67">
-        <v>67.47</v>
+        <v>68.508</v>
       </c>
       <c r="G67">
         <v>14.7</v>
@@ -6781,37 +6781,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M67">
-        <v>9.904596000000002</v>
+        <v>10.0569744</v>
       </c>
       <c r="N67">
-        <v>-1.324596</v>
+        <v>-1.476974399999998</v>
       </c>
       <c r="O67">
-        <v>-0.1324596</v>
+        <v>-0.1476974399999998</v>
       </c>
       <c r="P67">
-        <v>-1.1921364</v>
+        <v>-1.329276959999998</v>
       </c>
       <c r="Q67">
-        <v>6.5278636</v>
+        <v>6.390723040000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1705048596276463</v>
+        <v>0.1741726496166947</v>
       </c>
       <c r="T67">
-        <v>1.929144517541767</v>
+        <v>1.985884062175348</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.08662645099305415</v>
+        <v>0.08531392900831092</v>
       </c>
       <c r="W67">
-        <v>0.1340832369942197</v>
+        <v>0.13427591522158</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8662645099305414</v>
+        <v>0.8531392900831091</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.147840804915919</v>
+        <v>0.148850804915919</v>
       </c>
       <c r="C68">
-        <v>-12.18394903103693</v>
+        <v>-13.62990597531268</v>
       </c>
       <c r="D68">
-        <v>41.62405096896306</v>
+        <v>41.21609402468733</v>
       </c>
       <c r="E68">
-        <v>54.408</v>
+        <v>55.44600000000001</v>
       </c>
       <c r="F68">
-        <v>68.508</v>
+        <v>69.54600000000001</v>
       </c>
       <c r="G68">
         <v>14.7</v>
@@ -6863,37 +6863,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M68">
-        <v>10.0569744</v>
+        <v>10.2093528</v>
       </c>
       <c r="N68">
-        <v>-1.476974399999998</v>
+        <v>-1.629352799999999</v>
       </c>
       <c r="O68">
-        <v>-0.1476974399999998</v>
+        <v>-0.16293528</v>
       </c>
       <c r="P68">
-        <v>-1.329276959999998</v>
+        <v>-1.46641752</v>
       </c>
       <c r="Q68">
-        <v>6.390723040000002</v>
+        <v>6.25358248</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1741726496166947</v>
+        <v>0.1780627299081097</v>
       </c>
       <c r="T68">
-        <v>1.985884062175348</v>
+        <v>2.046062367089752</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.08531392900831092</v>
+        <v>0.08404058678430626</v>
       </c>
       <c r="W68">
-        <v>0.13427591522158</v>
+        <v>0.1344628418600639</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8531392900831091</v>
+        <v>0.8404058678430626</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.148850804915919</v>
+        <v>0.149860804915919</v>
       </c>
       <c r="C69">
-        <v>-13.62990597531268</v>
+        <v>-15.06794377050913</v>
       </c>
       <c r="D69">
-        <v>41.21609402468733</v>
+        <v>40.81605622949087</v>
       </c>
       <c r="E69">
-        <v>55.44600000000001</v>
+        <v>56.48400000000001</v>
       </c>
       <c r="F69">
-        <v>69.54600000000001</v>
+        <v>70.584</v>
       </c>
       <c r="G69">
         <v>14.7</v>
@@ -6945,37 +6945,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M69">
-        <v>10.2093528</v>
+        <v>10.3617312</v>
       </c>
       <c r="N69">
-        <v>-1.629352799999999</v>
+        <v>-1.781731199999999</v>
       </c>
       <c r="O69">
-        <v>-0.16293528</v>
+        <v>-0.17817312</v>
       </c>
       <c r="P69">
-        <v>-1.46641752</v>
+        <v>-1.60355808</v>
       </c>
       <c r="Q69">
-        <v>6.25358248</v>
+        <v>6.11644192</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1780627299081097</v>
+        <v>0.1821959402177382</v>
       </c>
       <c r="T69">
-        <v>2.046062367089752</v>
+        <v>2.110001816061307</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.08404058678430626</v>
+        <v>0.08280469580218411</v>
       </c>
       <c r="W69">
-        <v>0.1344628418600639</v>
+        <v>0.1346442706562394</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8404058678430626</v>
+        <v>0.828046958021841</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.149860804915919</v>
+        <v>0.150870804915919</v>
       </c>
       <c r="C70">
-        <v>-15.06794377050913</v>
+        <v>-16.49829078664528</v>
       </c>
       <c r="D70">
-        <v>40.81605622949087</v>
+        <v>40.42370921335471</v>
       </c>
       <c r="E70">
-        <v>56.48400000000001</v>
+        <v>57.52200000000001</v>
       </c>
       <c r="F70">
-        <v>70.584</v>
+        <v>71.622</v>
       </c>
       <c r="G70">
         <v>14.7</v>
@@ -7027,37 +7027,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M70">
-        <v>10.3617312</v>
+        <v>10.5141096</v>
       </c>
       <c r="N70">
-        <v>-1.781731199999999</v>
+        <v>-1.934109599999999</v>
       </c>
       <c r="O70">
-        <v>-0.17817312</v>
+        <v>-0.1934109599999999</v>
       </c>
       <c r="P70">
-        <v>-1.60355808</v>
+        <v>-1.740698639999999</v>
       </c>
       <c r="Q70">
-        <v>6.11644192</v>
+        <v>5.979301360000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1821959402177382</v>
+        <v>0.18659580925702</v>
       </c>
       <c r="T70">
-        <v>2.110001816061307</v>
+        <v>2.178066390772962</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.08280469580218411</v>
+        <v>0.08160462774707999</v>
       </c>
       <c r="W70">
-        <v>0.1346442706562394</v>
+        <v>0.1348204406467287</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.828046958021841</v>
+        <v>0.8160462774707999</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.150870804915919</v>
+        <v>0.151880804915919</v>
       </c>
       <c r="C71">
-        <v>-16.49829078664528</v>
+        <v>-17.92116669645623</v>
       </c>
       <c r="D71">
-        <v>40.42370921335471</v>
+        <v>40.03883330354379</v>
       </c>
       <c r="E71">
-        <v>57.52200000000001</v>
+        <v>58.56000000000002</v>
       </c>
       <c r="F71">
-        <v>71.622</v>
+        <v>72.66000000000001</v>
       </c>
       <c r="G71">
         <v>14.7</v>
@@ -7109,37 +7109,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M71">
-        <v>10.5141096</v>
+        <v>10.666488</v>
       </c>
       <c r="N71">
-        <v>-1.934109599999999</v>
+        <v>-2.086488000000001</v>
       </c>
       <c r="O71">
-        <v>-0.1934109599999999</v>
+        <v>-0.2086488000000001</v>
       </c>
       <c r="P71">
-        <v>-1.740698639999999</v>
+        <v>-1.877839200000001</v>
       </c>
       <c r="Q71">
-        <v>5.979301360000001</v>
+        <v>5.842160799999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.18659580925702</v>
+        <v>0.1912890028989207</v>
       </c>
       <c r="T71">
-        <v>2.178066390772962</v>
+        <v>2.250668603798728</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.08160462774707999</v>
+        <v>0.08043884735069312</v>
       </c>
       <c r="W71">
-        <v>0.1348204406467287</v>
+        <v>0.1349915772089182</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8160462774707999</v>
+        <v>0.8043884735069312</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.151880804915919</v>
+        <v>0.1919311542298997</v>
       </c>
       <c r="C72">
-        <v>-17.92116669645623</v>
+        <v>-29.93266012009928</v>
       </c>
       <c r="D72">
-        <v>40.03883330354379</v>
+        <v>29.06533987990073</v>
       </c>
       <c r="E72">
-        <v>58.56000000000002</v>
+        <v>59.59800000000001</v>
       </c>
       <c r="F72">
-        <v>72.66000000000001</v>
+        <v>73.69800000000001</v>
       </c>
       <c r="G72">
         <v>14.7</v>
@@ -7191,45 +7191,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M72">
-        <v>10.666488</v>
+        <v>14.7985584</v>
       </c>
       <c r="N72">
-        <v>-2.086488000000001</v>
+        <v>-6.218558400000001</v>
       </c>
       <c r="O72">
-        <v>-0.2086488000000001</v>
+        <v>-0.6218558400000002</v>
       </c>
       <c r="P72">
-        <v>-1.877839200000001</v>
+        <v>-5.596702560000001</v>
       </c>
       <c r="Q72">
-        <v>5.842160799999998</v>
+        <v>2.123297439999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1912890028989207</v>
+        <v>0.1987208627022654</v>
       </c>
       <c r="T72">
-        <v>2.250668603798728</v>
+        <v>2.36563711134182</v>
       </c>
       <c r="U72">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08043884735069312</v>
+        <v>0.05797862040399827</v>
       </c>
       <c r="W72">
-        <v>0.1349915772089182</v>
+        <v>0.1891578930228772</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8043884735069312</v>
+        <v>0.5797862040399827</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1919311542298997</v>
+        <v>0.1934811542298997</v>
       </c>
       <c r="C73">
-        <v>-29.93266012009926</v>
+        <v>-31.27571784428059</v>
       </c>
       <c r="D73">
-        <v>29.06533987990073</v>
+        <v>28.7602821557194</v>
       </c>
       <c r="E73">
-        <v>59.598</v>
+        <v>60.636</v>
       </c>
       <c r="F73">
-        <v>73.69799999999999</v>
+        <v>74.73599999999999</v>
       </c>
       <c r="G73">
         <v>14.7</v>
@@ -7273,37 +7273,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M73">
-        <v>14.7985584</v>
+        <v>15.0069888</v>
       </c>
       <c r="N73">
-        <v>-6.218558399999997</v>
+        <v>-6.426988799999997</v>
       </c>
       <c r="O73">
-        <v>-0.6218558399999998</v>
+        <v>-0.6426988799999998</v>
       </c>
       <c r="P73">
-        <v>-5.596702559999997</v>
+        <v>-5.784289919999997</v>
       </c>
       <c r="Q73">
-        <v>2.123297440000003</v>
+        <v>1.935710080000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1987208627022653</v>
+        <v>0.204182322084489</v>
       </c>
       <c r="T73">
-        <v>2.365637111341819</v>
+        <v>2.450124151032598</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05797862040399829</v>
+        <v>0.05717336178727609</v>
       </c>
       <c r="W73">
-        <v>0.1891578930228772</v>
+        <v>0.189319588953115</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5797862040399828</v>
+        <v>0.5717336178727609</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1934811542298997</v>
+        <v>0.1950311542298997</v>
       </c>
       <c r="C74">
-        <v>-31.27571784428059</v>
+        <v>-32.61243856095273</v>
       </c>
       <c r="D74">
-        <v>28.7602821557194</v>
+        <v>28.46156143904727</v>
       </c>
       <c r="E74">
-        <v>60.636</v>
+        <v>61.67400000000001</v>
       </c>
       <c r="F74">
-        <v>74.73599999999999</v>
+        <v>75.774</v>
       </c>
       <c r="G74">
         <v>14.7</v>
@@ -7355,37 +7355,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M74">
-        <v>15.0069888</v>
+        <v>15.2154192</v>
       </c>
       <c r="N74">
-        <v>-6.426988799999997</v>
+        <v>-6.635419199999999</v>
       </c>
       <c r="O74">
-        <v>-0.6426988799999998</v>
+        <v>-0.66354192</v>
       </c>
       <c r="P74">
-        <v>-5.784289919999997</v>
+        <v>-5.971877279999999</v>
       </c>
       <c r="Q74">
-        <v>1.935710080000002</v>
+        <v>1.74812272</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.204182322084489</v>
+        <v>0.2100483340135442</v>
       </c>
       <c r="T74">
-        <v>2.450124151032598</v>
+        <v>2.540869489959731</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05717336178727609</v>
+        <v>0.05639016505046408</v>
       </c>
       <c r="W74">
-        <v>0.189319588953115</v>
+        <v>0.1894768548578668</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5717336178727609</v>
+        <v>0.5639016505046408</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1950311542298997</v>
+        <v>0.1965811542298997</v>
       </c>
       <c r="C75">
-        <v>-32.61243856095273</v>
+        <v>-33.94301769961126</v>
       </c>
       <c r="D75">
-        <v>28.46156143904727</v>
+        <v>28.16898230038873</v>
       </c>
       <c r="E75">
-        <v>61.67400000000001</v>
+        <v>62.712</v>
       </c>
       <c r="F75">
-        <v>75.774</v>
+        <v>76.812</v>
       </c>
       <c r="G75">
         <v>14.7</v>
@@ -7437,37 +7437,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M75">
-        <v>15.2154192</v>
+        <v>15.4238496</v>
       </c>
       <c r="N75">
-        <v>-6.635419199999999</v>
+        <v>-6.843849599999999</v>
       </c>
       <c r="O75">
-        <v>-0.66354192</v>
+        <v>-0.6843849599999999</v>
       </c>
       <c r="P75">
-        <v>-5.971877279999999</v>
+        <v>-6.159464639999999</v>
       </c>
       <c r="Q75">
-        <v>1.74812272</v>
+        <v>1.560535360000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2100483340135442</v>
+        <v>0.2163655776294497</v>
       </c>
       <c r="T75">
-        <v>2.540869489959731</v>
+        <v>2.638595239573567</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05639016505046408</v>
+        <v>0.05562813579302538</v>
       </c>
       <c r="W75">
-        <v>0.1894768548578668</v>
+        <v>0.1896298703327605</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5639016505046408</v>
+        <v>0.5562813579302538</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1965811542298997</v>
+        <v>0.1981311542298997</v>
       </c>
       <c r="C76">
-        <v>-33.94301769961126</v>
+        <v>-35.26764273561478</v>
       </c>
       <c r="D76">
-        <v>28.16898230038873</v>
+        <v>27.88235726438522</v>
       </c>
       <c r="E76">
-        <v>62.712</v>
+        <v>63.75</v>
       </c>
       <c r="F76">
-        <v>76.812</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="G76">
         <v>14.7</v>
@@ -7519,37 +7519,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M76">
-        <v>15.4238496</v>
+        <v>15.63228</v>
       </c>
       <c r="N76">
-        <v>-6.843849599999999</v>
+        <v>-7.052279999999998</v>
       </c>
       <c r="O76">
-        <v>-0.6843849599999999</v>
+        <v>-0.7052279999999999</v>
       </c>
       <c r="P76">
-        <v>-6.159464639999999</v>
+        <v>-6.347051999999998</v>
       </c>
       <c r="Q76">
-        <v>1.560535360000001</v>
+        <v>1.372948000000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2163655776294497</v>
+        <v>0.2231882007346277</v>
       </c>
       <c r="T76">
-        <v>2.638595239573567</v>
+        <v>2.74413904915651</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.05562813579302538</v>
+        <v>0.05488642731578505</v>
       </c>
       <c r="W76">
-        <v>0.1896298703327605</v>
+        <v>0.1897788053949904</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5562813579302538</v>
+        <v>0.5488642731578504</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1981311542298997</v>
+        <v>0.1996811542298997</v>
       </c>
       <c r="C77">
-        <v>-35.26764273561478</v>
+        <v>-36.58649359078338</v>
       </c>
       <c r="D77">
-        <v>27.88235726438522</v>
+        <v>27.60150640921662</v>
       </c>
       <c r="E77">
-        <v>63.75</v>
+        <v>64.78800000000001</v>
       </c>
       <c r="F77">
-        <v>77.84999999999999</v>
+        <v>78.88800000000001</v>
       </c>
       <c r="G77">
         <v>14.7</v>
@@ -7601,37 +7601,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M77">
-        <v>15.63228</v>
+        <v>15.8407104</v>
       </c>
       <c r="N77">
-        <v>-7.052279999999998</v>
+        <v>-7.260710399999999</v>
       </c>
       <c r="O77">
-        <v>-0.7052279999999999</v>
+        <v>-0.7260710399999999</v>
       </c>
       <c r="P77">
-        <v>-6.347051999999998</v>
+        <v>-6.534639359999999</v>
       </c>
       <c r="Q77">
-        <v>1.372948000000002</v>
+        <v>1.185360640000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2231882007346277</v>
+        <v>0.2305793757652372</v>
       </c>
       <c r="T77">
-        <v>2.74413904915651</v>
+        <v>2.858478176204698</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05488642731578505</v>
+        <v>0.05416423748268261</v>
       </c>
       <c r="W77">
-        <v>0.1897788053949904</v>
+        <v>0.1899238211134773</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5488642731578504</v>
+        <v>0.541642374826826</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1996811542298997</v>
+        <v>0.2012311542298997</v>
       </c>
       <c r="C78">
-        <v>-36.58649359078338</v>
+        <v>-37.8997430100279</v>
       </c>
       <c r="D78">
-        <v>27.60150640921662</v>
+        <v>27.3262569899721</v>
       </c>
       <c r="E78">
-        <v>64.78800000000001</v>
+        <v>65.82600000000001</v>
       </c>
       <c r="F78">
-        <v>78.88800000000001</v>
+        <v>79.926</v>
       </c>
       <c r="G78">
         <v>14.7</v>
@@ -7683,37 +7683,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M78">
-        <v>15.8407104</v>
+        <v>16.0491408</v>
       </c>
       <c r="N78">
-        <v>-7.260710399999999</v>
+        <v>-7.469140799999998</v>
       </c>
       <c r="O78">
-        <v>-0.7260710399999999</v>
+        <v>-0.7469140799999998</v>
       </c>
       <c r="P78">
-        <v>-6.534639359999999</v>
+        <v>-6.722226719999998</v>
       </c>
       <c r="Q78">
-        <v>1.185360640000001</v>
+        <v>0.9977732800000014</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2305793757652372</v>
+        <v>0.2386132616680736</v>
       </c>
       <c r="T78">
-        <v>2.858478176204698</v>
+        <v>2.982759836039685</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.05416423748268261</v>
+        <v>0.05346080582706336</v>
       </c>
       <c r="W78">
-        <v>0.1899238211134773</v>
+        <v>0.1900650701899257</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.541642374826826</v>
+        <v>0.5346080582706335</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2012311542298997</v>
+        <v>0.2027811542298997</v>
       </c>
       <c r="C79">
-        <v>-37.8997430100279</v>
+        <v>-39.20755691566671</v>
       </c>
       <c r="D79">
-        <v>27.3262569899721</v>
+        <v>27.05644308433329</v>
       </c>
       <c r="E79">
-        <v>65.82600000000001</v>
+        <v>66.864</v>
       </c>
       <c r="F79">
-        <v>79.926</v>
+        <v>80.964</v>
       </c>
       <c r="G79">
         <v>14.7</v>
@@ -7765,37 +7765,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M79">
-        <v>16.0491408</v>
+        <v>16.2575712</v>
       </c>
       <c r="N79">
-        <v>-7.469140799999998</v>
+        <v>-7.677571199999999</v>
       </c>
       <c r="O79">
-        <v>-0.7469140799999998</v>
+        <v>-0.76775712</v>
       </c>
       <c r="P79">
-        <v>-6.722226719999998</v>
+        <v>-6.909814079999999</v>
       </c>
       <c r="Q79">
-        <v>0.9977732800000014</v>
+        <v>0.8101859200000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2386132616680736</v>
+        <v>0.2473775008348043</v>
       </c>
       <c r="T79">
-        <v>2.982759836039685</v>
+        <v>3.118339828586944</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.05346080582706336</v>
+        <v>0.05277541088056253</v>
       </c>
       <c r="W79">
-        <v>0.1900650701899257</v>
+        <v>0.1902026974951831</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5346080582706335</v>
+        <v>0.5277541088056253</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2027811542298997</v>
+        <v>0.2043311542298997</v>
       </c>
       <c r="C80">
-        <v>-39.20755691566671</v>
+        <v>-40.51009474095686</v>
       </c>
       <c r="D80">
-        <v>27.05644308433329</v>
+        <v>26.79190525904314</v>
       </c>
       <c r="E80">
-        <v>66.864</v>
+        <v>67.902</v>
       </c>
       <c r="F80">
-        <v>80.964</v>
+        <v>82.002</v>
       </c>
       <c r="G80">
         <v>14.7</v>
@@ -7847,37 +7847,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M80">
-        <v>16.2575712</v>
+        <v>16.4660016</v>
       </c>
       <c r="N80">
-        <v>-7.677571199999999</v>
+        <v>-7.886001599999997</v>
       </c>
       <c r="O80">
-        <v>-0.76775712</v>
+        <v>-0.7886001599999997</v>
       </c>
       <c r="P80">
-        <v>-6.909814079999999</v>
+        <v>-7.097401439999997</v>
       </c>
       <c r="Q80">
-        <v>0.8101859200000003</v>
+        <v>0.6225985600000028</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2473775008348043</v>
+        <v>0.2569764294459854</v>
       </c>
       <c r="T80">
-        <v>3.118339828586944</v>
+        <v>3.266832201376798</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.05277541088056253</v>
+        <v>0.05210736770485922</v>
       </c>
       <c r="W80">
-        <v>0.1902026974951831</v>
+        <v>0.1903368405648643</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5277541088056253</v>
+        <v>0.5210736770485922</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2043311542298997</v>
+        <v>0.2058811542298997</v>
       </c>
       <c r="C81">
-        <v>-40.51009474095686</v>
+        <v>-41.80750974424875</v>
       </c>
       <c r="D81">
-        <v>26.79190525904314</v>
+        <v>26.53249025575126</v>
       </c>
       <c r="E81">
-        <v>67.902</v>
+        <v>68.94000000000001</v>
       </c>
       <c r="F81">
-        <v>82.002</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="G81">
         <v>14.7</v>
@@ -7929,37 +7929,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M81">
-        <v>16.4660016</v>
+        <v>16.674432</v>
       </c>
       <c r="N81">
-        <v>-7.886001599999997</v>
+        <v>-8.094432000000001</v>
       </c>
       <c r="O81">
-        <v>-0.7886001599999997</v>
+        <v>-0.8094432000000001</v>
       </c>
       <c r="P81">
-        <v>-7.097401439999997</v>
+        <v>-7.284988800000001</v>
       </c>
       <c r="Q81">
-        <v>0.6225985600000028</v>
+        <v>0.435011199999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2569764294459854</v>
+        <v>0.2675352509182847</v>
       </c>
       <c r="T81">
-        <v>3.266832201376798</v>
+        <v>3.430173811445639</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.05210736770485922</v>
+        <v>0.05145602560854846</v>
       </c>
       <c r="W81">
-        <v>0.1903368405648643</v>
+        <v>0.1904676300578035</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5210736770485922</v>
+        <v>0.5145602560854847</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2058811542298997</v>
+        <v>0.2074311542298997</v>
       </c>
       <c r="C82">
-        <v>-41.80750974424875</v>
+        <v>-43.09994930506459</v>
       </c>
       <c r="D82">
-        <v>26.53249025575126</v>
+        <v>26.27805069493541</v>
       </c>
       <c r="E82">
-        <v>68.94000000000001</v>
+        <v>69.97800000000001</v>
       </c>
       <c r="F82">
-        <v>83.04000000000001</v>
+        <v>84.078</v>
       </c>
       <c r="G82">
         <v>14.7</v>
@@ -8011,37 +8011,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M82">
-        <v>16.674432</v>
+        <v>16.8828624</v>
       </c>
       <c r="N82">
-        <v>-8.094432000000001</v>
+        <v>-8.302862399999999</v>
       </c>
       <c r="O82">
-        <v>-0.8094432000000001</v>
+        <v>-0.83028624</v>
       </c>
       <c r="P82">
-        <v>-7.284988800000001</v>
+        <v>-7.472576159999999</v>
       </c>
       <c r="Q82">
-        <v>0.435011199999999</v>
+        <v>0.2474238400000006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2675352509182847</v>
+        <v>0.2792055272824049</v>
       </c>
       <c r="T82">
-        <v>3.430173811445639</v>
+        <v>3.610709275205935</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.05145602560854846</v>
+        <v>0.0508207660331343</v>
       </c>
       <c r="W82">
-        <v>0.1904676300578035</v>
+        <v>0.1905951901805466</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5145602560854847</v>
+        <v>0.508207660331343</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2074311542298997</v>
+        <v>0.2089811542298997</v>
       </c>
       <c r="C83">
-        <v>-43.09994930506459</v>
+        <v>-44.38755520330309</v>
       </c>
       <c r="D83">
-        <v>26.27805069493541</v>
+        <v>26.02844479669691</v>
       </c>
       <c r="E83">
-        <v>69.97800000000001</v>
+        <v>71.01600000000001</v>
       </c>
       <c r="F83">
-        <v>84.078</v>
+        <v>85.116</v>
       </c>
       <c r="G83">
         <v>14.7</v>
@@ -8093,37 +8093,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M83">
-        <v>16.8828624</v>
+        <v>17.0912928</v>
       </c>
       <c r="N83">
-        <v>-8.302862399999999</v>
+        <v>-8.5112928</v>
       </c>
       <c r="O83">
-        <v>-0.83028624</v>
+        <v>-0.85112928</v>
       </c>
       <c r="P83">
-        <v>-7.472576159999999</v>
+        <v>-7.660163519999999</v>
       </c>
       <c r="Q83">
-        <v>0.2474238400000006</v>
+        <v>0.05983648000000041</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2792055272824049</v>
+        <v>0.2921725010203163</v>
       </c>
       <c r="T83">
-        <v>3.610709275205935</v>
+        <v>3.811304234939599</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.0508207660331343</v>
+        <v>0.05020100059370583</v>
       </c>
       <c r="W83">
-        <v>0.1905951901805466</v>
+        <v>0.1907196390807839</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.508207660331343</v>
+        <v>0.5020100059370582</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2089811542298997</v>
+        <v>0.2398637536373726</v>
       </c>
       <c r="C84">
-        <v>-44.38755520330309</v>
+        <v>-49.56762717083775</v>
       </c>
       <c r="D84">
-        <v>26.02844479669691</v>
+        <v>21.88637282916226</v>
       </c>
       <c r="E84">
-        <v>71.01600000000001</v>
+        <v>72.05400000000002</v>
       </c>
       <c r="F84">
-        <v>85.116</v>
+        <v>86.15400000000001</v>
       </c>
       <c r="G84">
         <v>14.7</v>
@@ -8175,45 +8175,45 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M84">
-        <v>17.0912928</v>
+        <v>20.3151132</v>
       </c>
       <c r="N84">
-        <v>-8.5112928</v>
+        <v>-11.7351132</v>
       </c>
       <c r="O84">
-        <v>-0.85112928</v>
+        <v>-1.17351132</v>
       </c>
       <c r="P84">
-        <v>-7.660163519999999</v>
+        <v>-10.56160188</v>
       </c>
       <c r="Q84">
-        <v>0.05983648000000041</v>
+        <v>-2.841601880000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2921725010203163</v>
+        <v>0.3083273505360575</v>
       </c>
       <c r="T84">
-        <v>3.811304234939599</v>
+        <v>4.061214619090299</v>
       </c>
       <c r="U84">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05020100059370583</v>
+        <v>0.04223456652951361</v>
       </c>
       <c r="W84">
-        <v>0.1907196390807839</v>
+        <v>0.2258410892123407</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5020100059370582</v>
+        <v>0.4223456652951361</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2398637536373726</v>
+        <v>0.2417637536373725</v>
       </c>
       <c r="C85">
-        <v>-49.56762717083775</v>
+        <v>-50.81783023188116</v>
       </c>
       <c r="D85">
-        <v>21.88637282916226</v>
+        <v>21.67416976811884</v>
       </c>
       <c r="E85">
-        <v>72.05400000000002</v>
+        <v>73.09200000000001</v>
       </c>
       <c r="F85">
-        <v>86.15400000000001</v>
+        <v>87.19200000000001</v>
       </c>
       <c r="G85">
         <v>14.7</v>
@@ -8257,37 +8257,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M85">
-        <v>20.3151132</v>
+        <v>20.5598736</v>
       </c>
       <c r="N85">
-        <v>-11.7351132</v>
+        <v>-11.9798736</v>
       </c>
       <c r="O85">
-        <v>-1.17351132</v>
+        <v>-1.19798736</v>
       </c>
       <c r="P85">
-        <v>-10.56160188</v>
+        <v>-10.78188624</v>
       </c>
       <c r="Q85">
-        <v>-2.841601880000002</v>
+        <v>-3.061886240000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3083273505360575</v>
+        <v>0.3247353099445611</v>
       </c>
       <c r="T85">
-        <v>4.061214619090299</v>
+        <v>4.315040532783443</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04223456652951361</v>
+        <v>0.04173177407082893</v>
       </c>
       <c r="W85">
-        <v>0.2258410892123407</v>
+        <v>0.2259596476740985</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4223456652951361</v>
+        <v>0.4173177407082892</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2417637536373725</v>
+        <v>0.2436637536373725</v>
       </c>
       <c r="C86">
-        <v>-50.81783023188116</v>
+        <v>-52.06395790459729</v>
       </c>
       <c r="D86">
-        <v>21.67416976811884</v>
+        <v>21.4660420954027</v>
       </c>
       <c r="E86">
-        <v>73.092</v>
+        <v>74.13</v>
       </c>
       <c r="F86">
-        <v>87.19199999999999</v>
+        <v>88.22999999999999</v>
       </c>
       <c r="G86">
         <v>14.7</v>
@@ -8339,37 +8339,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M86">
-        <v>20.5598736</v>
+        <v>20.804634</v>
       </c>
       <c r="N86">
-        <v>-11.9798736</v>
+        <v>-12.224634</v>
       </c>
       <c r="O86">
-        <v>-1.19798736</v>
+        <v>-1.2224634</v>
       </c>
       <c r="P86">
-        <v>-10.78188624</v>
+        <v>-11.0021706</v>
       </c>
       <c r="Q86">
-        <v>-3.061886239999999</v>
+        <v>-3.282170599999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3247353099445609</v>
+        <v>0.3433309972741984</v>
       </c>
       <c r="T86">
-        <v>4.31504053278344</v>
+        <v>4.60270990163567</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04173177407082893</v>
+        <v>0.04124081202293683</v>
       </c>
       <c r="W86">
-        <v>0.2259596476740985</v>
+        <v>0.2260754165249915</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4173177407082893</v>
+        <v>0.4124081202293682</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2436637536373725</v>
+        <v>0.2455637536373725</v>
       </c>
       <c r="C87">
-        <v>-52.06395790459729</v>
+        <v>-53.30612647491413</v>
       </c>
       <c r="D87">
-        <v>21.4660420954027</v>
+        <v>21.26187352508587</v>
       </c>
       <c r="E87">
-        <v>74.13</v>
+        <v>75.16800000000001</v>
       </c>
       <c r="F87">
-        <v>88.22999999999999</v>
+        <v>89.268</v>
       </c>
       <c r="G87">
         <v>14.7</v>
@@ -8421,37 +8421,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M87">
-        <v>20.804634</v>
+        <v>21.0493944</v>
       </c>
       <c r="N87">
-        <v>-12.224634</v>
+        <v>-12.4693944</v>
       </c>
       <c r="O87">
-        <v>-1.2224634</v>
+        <v>-1.24693944</v>
       </c>
       <c r="P87">
-        <v>-11.0021706</v>
+        <v>-11.22245496</v>
       </c>
       <c r="Q87">
-        <v>-3.282170599999998</v>
+        <v>-3.502454959999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3433309972741984</v>
+        <v>0.3645832113652125</v>
       </c>
       <c r="T87">
-        <v>4.60270990163567</v>
+        <v>4.931474894609646</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04124081202293683</v>
+        <v>0.04076126769708872</v>
       </c>
       <c r="W87">
-        <v>0.2260754165249915</v>
+        <v>0.2261884930770265</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4124081202293682</v>
+        <v>0.4076126769708872</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2455637536373725</v>
+        <v>0.2474637536373726</v>
       </c>
       <c r="C88">
-        <v>-53.30612647491413</v>
+        <v>-54.54444784635059</v>
       </c>
       <c r="D88">
-        <v>21.26187352508587</v>
+        <v>21.06155215364941</v>
       </c>
       <c r="E88">
-        <v>75.16800000000001</v>
+        <v>76.206</v>
       </c>
       <c r="F88">
-        <v>89.268</v>
+        <v>90.306</v>
       </c>
       <c r="G88">
         <v>14.7</v>
@@ -8503,37 +8503,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M88">
-        <v>21.0493944</v>
+        <v>21.2941548</v>
       </c>
       <c r="N88">
-        <v>-12.4693944</v>
+        <v>-12.7141548</v>
       </c>
       <c r="O88">
-        <v>-1.24693944</v>
+        <v>-1.27141548</v>
       </c>
       <c r="P88">
-        <v>-11.22245496</v>
+        <v>-11.44273932</v>
       </c>
       <c r="Q88">
-        <v>-3.502454959999999</v>
+        <v>-3.72273932</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3645832113652125</v>
+        <v>0.3891049968548442</v>
       </c>
       <c r="T88">
-        <v>4.931474894609646</v>
+        <v>5.310819117271927</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04076126769708872</v>
+        <v>0.04029274737873138</v>
       </c>
       <c r="W88">
-        <v>0.2261884930770265</v>
+        <v>0.2262989701680952</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4076126769708872</v>
+        <v>0.4029274737873138</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2474637536373726</v>
+        <v>0.2493637536373725</v>
       </c>
       <c r="C89">
-        <v>-54.54444784635059</v>
+        <v>-55.77902974453673</v>
       </c>
       <c r="D89">
-        <v>21.06155215364941</v>
+        <v>20.86497025546326</v>
       </c>
       <c r="E89">
-        <v>76.206</v>
+        <v>77.244</v>
       </c>
       <c r="F89">
-        <v>90.306</v>
+        <v>91.34399999999999</v>
       </c>
       <c r="G89">
         <v>14.7</v>
@@ -8585,37 +8585,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M89">
-        <v>21.2941548</v>
+        <v>21.5389152</v>
       </c>
       <c r="N89">
-        <v>-12.7141548</v>
+        <v>-12.9589152</v>
       </c>
       <c r="O89">
-        <v>-1.27141548</v>
+        <v>-1.29589152</v>
       </c>
       <c r="P89">
-        <v>-11.44273932</v>
+        <v>-11.66302368</v>
       </c>
       <c r="Q89">
-        <v>-3.72273932</v>
+        <v>-3.943023679999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3891049968548442</v>
+        <v>0.417713746592748</v>
       </c>
       <c r="T89">
-        <v>5.310819117271927</v>
+        <v>5.753387377044588</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04029274737873138</v>
+        <v>0.03983487524942762</v>
       </c>
       <c r="W89">
-        <v>0.2262989701680952</v>
+        <v>0.226406936416185</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4029274737873138</v>
+        <v>0.3983487524942761</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2493637536373725</v>
+        <v>0.2512637536373725</v>
       </c>
       <c r="C90">
-        <v>-55.77902974453673</v>
+        <v>-57.00997591038626</v>
       </c>
       <c r="D90">
-        <v>20.86497025546326</v>
+        <v>20.67202408961374</v>
       </c>
       <c r="E90">
-        <v>77.244</v>
+        <v>78.28200000000001</v>
       </c>
       <c r="F90">
-        <v>91.34399999999999</v>
+        <v>92.38200000000001</v>
       </c>
       <c r="G90">
         <v>14.7</v>
@@ -8667,37 +8667,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M90">
-        <v>21.5389152</v>
+        <v>21.7836756</v>
       </c>
       <c r="N90">
-        <v>-12.9589152</v>
+        <v>-13.2036756</v>
       </c>
       <c r="O90">
-        <v>-1.29589152</v>
+        <v>-1.32036756</v>
       </c>
       <c r="P90">
-        <v>-11.66302368</v>
+        <v>-11.88330804</v>
       </c>
       <c r="Q90">
-        <v>-3.943023679999997</v>
+        <v>-4.16330804</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.417713746592748</v>
+        <v>0.4515240871920886</v>
       </c>
       <c r="T90">
-        <v>5.753387377044588</v>
+        <v>6.27642259313955</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03983487524942762</v>
+        <v>0.03938729238145652</v>
       </c>
       <c r="W90">
-        <v>0.226406936416185</v>
+        <v>0.2265124764564526</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3983487524942761</v>
+        <v>0.3938729238145651</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2512637536373725</v>
+        <v>0.2531637536373725</v>
       </c>
       <c r="C91">
-        <v>-57.00997591038626</v>
+        <v>-58.23738628264906</v>
       </c>
       <c r="D91">
-        <v>20.67202408961374</v>
+        <v>20.48261371735094</v>
       </c>
       <c r="E91">
-        <v>78.28200000000001</v>
+        <v>79.32000000000001</v>
       </c>
       <c r="F91">
-        <v>92.38200000000001</v>
+        <v>93.42</v>
       </c>
       <c r="G91">
         <v>14.7</v>
@@ -8749,37 +8749,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M91">
-        <v>21.7836756</v>
+        <v>22.028436</v>
       </c>
       <c r="N91">
-        <v>-13.2036756</v>
+        <v>-13.448436</v>
       </c>
       <c r="O91">
-        <v>-1.32036756</v>
+        <v>-1.3448436</v>
       </c>
       <c r="P91">
-        <v>-11.88330804</v>
+        <v>-12.1035924</v>
       </c>
       <c r="Q91">
-        <v>-4.16330804</v>
+        <v>-4.3835924</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4515240871920886</v>
+        <v>0.4920964959112976</v>
       </c>
       <c r="T91">
-        <v>6.27642259313955</v>
+        <v>6.904064852453507</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03938729238145652</v>
+        <v>0.03894965579944033</v>
       </c>
       <c r="W91">
-        <v>0.2265124764564526</v>
+        <v>0.226615671162492</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3938729238145651</v>
+        <v>0.3894965579944033</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2531637536373725</v>
+        <v>0.2550637536373725</v>
       </c>
       <c r="C92">
-        <v>-58.23738628264906</v>
+        <v>-59.46135717051914</v>
       </c>
       <c r="D92">
-        <v>20.48261371735094</v>
+        <v>20.29664282948086</v>
       </c>
       <c r="E92">
-        <v>79.32000000000001</v>
+        <v>80.358</v>
       </c>
       <c r="F92">
-        <v>93.42</v>
+        <v>94.458</v>
       </c>
       <c r="G92">
         <v>14.7</v>
@@ -8831,37 +8831,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M92">
-        <v>22.028436</v>
+        <v>22.2731964</v>
       </c>
       <c r="N92">
-        <v>-13.448436</v>
+        <v>-13.6931964</v>
       </c>
       <c r="O92">
-        <v>-1.3448436</v>
+        <v>-1.36931964</v>
       </c>
       <c r="P92">
-        <v>-12.1035924</v>
+        <v>-12.32387676</v>
       </c>
       <c r="Q92">
-        <v>-4.3835924</v>
+        <v>-4.603876759999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4920964959112976</v>
+        <v>0.5416849954569973</v>
       </c>
       <c r="T92">
-        <v>6.904064852453507</v>
+        <v>7.671183169392786</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03894965579944033</v>
+        <v>0.03852163760384208</v>
       </c>
       <c r="W92">
-        <v>0.226615671162492</v>
+        <v>0.226716597853014</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3894965579944033</v>
+        <v>0.3852163760384208</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2550637536373725</v>
+        <v>0.2569637536373726</v>
       </c>
       <c r="C93">
-        <v>-59.46135717051914</v>
+        <v>-60.68198141692383</v>
       </c>
       <c r="D93">
-        <v>20.29664282948086</v>
+        <v>20.11401858307616</v>
       </c>
       <c r="E93">
-        <v>80.358</v>
+        <v>81.396</v>
       </c>
       <c r="F93">
-        <v>94.458</v>
+        <v>95.496</v>
       </c>
       <c r="G93">
         <v>14.7</v>
@@ -8913,37 +8913,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M93">
-        <v>22.2731964</v>
+        <v>22.5179568</v>
       </c>
       <c r="N93">
-        <v>-13.6931964</v>
+        <v>-13.9379568</v>
       </c>
       <c r="O93">
-        <v>-1.36931964</v>
+        <v>-1.39379568</v>
       </c>
       <c r="P93">
-        <v>-12.32387676</v>
+        <v>-12.54416112</v>
       </c>
       <c r="Q93">
-        <v>-4.603876759999998</v>
+        <v>-4.824161119999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5416849954569973</v>
+        <v>0.6036706198891221</v>
       </c>
       <c r="T93">
-        <v>7.671183169392786</v>
+        <v>8.630081065566886</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03852163760384208</v>
+        <v>0.03810292415162642</v>
       </c>
       <c r="W93">
-        <v>0.226716597853014</v>
+        <v>0.2268153304850465</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3852163760384208</v>
+        <v>0.3810292415162642</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2569637536373726</v>
+        <v>0.2588637536373725</v>
       </c>
       <c r="C94">
-        <v>-60.68198141692383</v>
+        <v>-61.89934855307638</v>
       </c>
       <c r="D94">
-        <v>20.11401858307616</v>
+        <v>19.93465144692363</v>
       </c>
       <c r="E94">
-        <v>81.396</v>
+        <v>82.43400000000001</v>
       </c>
       <c r="F94">
-        <v>95.496</v>
+        <v>96.53400000000001</v>
       </c>
       <c r="G94">
         <v>14.7</v>
@@ -8995,37 +8995,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M94">
-        <v>22.5179568</v>
+        <v>22.7627172</v>
       </c>
       <c r="N94">
-        <v>-13.9379568</v>
+        <v>-14.1827172</v>
       </c>
       <c r="O94">
-        <v>-1.39379568</v>
+        <v>-1.41827172</v>
       </c>
       <c r="P94">
-        <v>-12.54416112</v>
+        <v>-12.76444548</v>
       </c>
       <c r="Q94">
-        <v>-4.824161119999999</v>
+        <v>-5.044445479999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6036706198891221</v>
+        <v>0.6833664227304255</v>
       </c>
       <c r="T94">
-        <v>8.630081065566886</v>
+        <v>9.8629497892193</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03810292415162642</v>
+        <v>0.03769321528978097</v>
       </c>
       <c r="W94">
-        <v>0.2268153304850465</v>
+        <v>0.2269119398346696</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3810292415162642</v>
+        <v>0.3769321528978097</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2588637536373725</v>
+        <v>0.2607637536373726</v>
       </c>
       <c r="C95">
-        <v>-61.89934855307638</v>
+        <v>-63.11354494483203</v>
       </c>
       <c r="D95">
-        <v>19.93465144692363</v>
+        <v>19.75845505516798</v>
       </c>
       <c r="E95">
-        <v>82.43400000000001</v>
+        <v>83.47200000000001</v>
       </c>
       <c r="F95">
-        <v>96.53400000000001</v>
+        <v>97.572</v>
       </c>
       <c r="G95">
         <v>14.7</v>
@@ -9077,37 +9077,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M95">
-        <v>22.7627172</v>
+        <v>23.0074776</v>
       </c>
       <c r="N95">
-        <v>-14.1827172</v>
+        <v>-14.4274776</v>
       </c>
       <c r="O95">
-        <v>-1.41827172</v>
+        <v>-1.44274776</v>
       </c>
       <c r="P95">
-        <v>-12.76444548</v>
+        <v>-12.98472984</v>
       </c>
       <c r="Q95">
-        <v>-5.044445479999999</v>
+        <v>-5.26472984</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6833664227304255</v>
+        <v>0.7896274931854966</v>
       </c>
       <c r="T95">
-        <v>9.8629497892193</v>
+        <v>11.50677475408919</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03769321528978097</v>
+        <v>0.03729222363776202</v>
       </c>
       <c r="W95">
-        <v>0.2269119398346696</v>
+        <v>0.2270064936662157</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3769321528978097</v>
+        <v>0.3729222363776201</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2607637536373726</v>
+        <v>0.2626637536373725</v>
       </c>
       <c r="C96">
-        <v>-63.11354494483203</v>
+        <v>-64.32465393135078</v>
       </c>
       <c r="D96">
-        <v>19.75845505516798</v>
+        <v>19.58534606864922</v>
       </c>
       <c r="E96">
-        <v>83.47200000000001</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="F96">
-        <v>97.572</v>
+        <v>98.61</v>
       </c>
       <c r="G96">
         <v>14.7</v>
@@ -9159,37 +9159,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M96">
-        <v>23.0074776</v>
+        <v>23.252238</v>
       </c>
       <c r="N96">
-        <v>-14.4274776</v>
+        <v>-14.672238</v>
       </c>
       <c r="O96">
-        <v>-1.44274776</v>
+        <v>-1.4672238</v>
       </c>
       <c r="P96">
-        <v>-12.98472984</v>
+        <v>-13.2050142</v>
       </c>
       <c r="Q96">
-        <v>-5.26472984</v>
+        <v>-5.485014200000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7896274931854966</v>
+        <v>0.9383929918225964</v>
       </c>
       <c r="T96">
-        <v>11.50677475408919</v>
+        <v>13.80812970490703</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03729222363776202</v>
+        <v>0.03689967391525926</v>
       </c>
       <c r="W96">
-        <v>0.2270064936662157</v>
+        <v>0.2270990568907819</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3729222363776201</v>
+        <v>0.3689967391525926</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2626637536373725</v>
+        <v>0.2645637536373726</v>
       </c>
       <c r="C97">
-        <v>-64.32465393135078</v>
+        <v>-65.53275595653416</v>
       </c>
       <c r="D97">
-        <v>19.58534606864922</v>
+        <v>19.41524404346585</v>
       </c>
       <c r="E97">
-        <v>84.51000000000001</v>
+        <v>85.54800000000002</v>
       </c>
       <c r="F97">
-        <v>98.61</v>
+        <v>99.64800000000001</v>
       </c>
       <c r="G97">
         <v>14.7</v>
@@ -9241,37 +9241,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M97">
-        <v>23.252238</v>
+        <v>23.4969984</v>
       </c>
       <c r="N97">
-        <v>-14.672238</v>
+        <v>-14.9169984</v>
       </c>
       <c r="O97">
-        <v>-1.4672238</v>
+        <v>-1.49169984</v>
       </c>
       <c r="P97">
-        <v>-13.2050142</v>
+        <v>-13.42529856</v>
       </c>
       <c r="Q97">
-        <v>-5.485014200000001</v>
+        <v>-5.70529856</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9383929918225964</v>
+        <v>1.161541239778246</v>
       </c>
       <c r="T97">
-        <v>13.80812970490703</v>
+        <v>17.2601621311338</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03689967391525926</v>
+        <v>0.03651530231197531</v>
       </c>
       <c r="W97">
-        <v>0.2270990568907819</v>
+        <v>0.2271896917148362</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3689967391525926</v>
+        <v>0.3651530231197531</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2645637536373726</v>
+        <v>0.2664637536373725</v>
       </c>
       <c r="C98">
-        <v>-65.53275595653415</v>
+        <v>-66.73792869367161</v>
       </c>
       <c r="D98">
-        <v>19.41524404346585</v>
+        <v>19.24807130632839</v>
       </c>
       <c r="E98">
-        <v>85.548</v>
+        <v>86.586</v>
       </c>
       <c r="F98">
-        <v>99.648</v>
+        <v>100.686</v>
       </c>
       <c r="G98">
         <v>14.7</v>
@@ -9323,37 +9323,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M98">
-        <v>23.4969984</v>
+        <v>23.7417588</v>
       </c>
       <c r="N98">
-        <v>-14.9169984</v>
+        <v>-15.1617588</v>
       </c>
       <c r="O98">
-        <v>-1.49169984</v>
+        <v>-1.51617588</v>
       </c>
       <c r="P98">
-        <v>-13.42529856</v>
+        <v>-13.64558292</v>
       </c>
       <c r="Q98">
-        <v>-5.705298559999998</v>
+        <v>-5.925582919999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.161541239778243</v>
+        <v>1.533454986370991</v>
       </c>
       <c r="T98">
-        <v>17.26016213113375</v>
+        <v>23.01354950817833</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03651530231197531</v>
+        <v>0.03613885589638794</v>
       </c>
       <c r="W98">
-        <v>0.2271896917148362</v>
+        <v>0.2272784577796317</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3651530231197532</v>
+        <v>0.3613885589638793</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2664637536373725</v>
+        <v>0.2683637536373726</v>
       </c>
       <c r="C99">
-        <v>-66.73792869367161</v>
+        <v>-67.94024716370248</v>
       </c>
       <c r="D99">
-        <v>19.24807130632839</v>
+        <v>19.08375283629751</v>
       </c>
       <c r="E99">
-        <v>86.586</v>
+        <v>87.624</v>
       </c>
       <c r="F99">
-        <v>100.686</v>
+        <v>101.724</v>
       </c>
       <c r="G99">
         <v>14.7</v>
@@ -9405,37 +9405,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M99">
-        <v>23.7417588</v>
+        <v>23.9865192</v>
       </c>
       <c r="N99">
-        <v>-15.1617588</v>
+        <v>-15.4065192</v>
       </c>
       <c r="O99">
-        <v>-1.51617588</v>
+        <v>-1.54065192</v>
       </c>
       <c r="P99">
-        <v>-13.64558292</v>
+        <v>-13.86586728</v>
       </c>
       <c r="Q99">
-        <v>-5.925582919999997</v>
+        <v>-6.145867279999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.533454986370991</v>
+        <v>2.277282479556486</v>
       </c>
       <c r="T99">
-        <v>23.01354950817833</v>
+        <v>34.5203242622675</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03613885589638794</v>
+        <v>0.03577009206071051</v>
       </c>
       <c r="W99">
-        <v>0.2272784577796317</v>
+        <v>0.2273654122920845</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3613885589638793</v>
+        <v>0.3577009206071051</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2683637536373726</v>
+        <v>0.2702637536373725</v>
       </c>
       <c r="C100">
-        <v>-67.94024716370248</v>
+        <v>-69.13978384747169</v>
       </c>
       <c r="D100">
-        <v>19.08375283629751</v>
+        <v>18.92221615252831</v>
       </c>
       <c r="E100">
-        <v>87.624</v>
+        <v>88.66200000000001</v>
       </c>
       <c r="F100">
-        <v>101.724</v>
+        <v>102.762</v>
       </c>
       <c r="G100">
         <v>14.7</v>
@@ -9487,37 +9487,37 @@
         <v>8.580000000000002</v>
       </c>
       <c r="M100">
-        <v>23.9865192</v>
+        <v>24.2312796</v>
       </c>
       <c r="N100">
-        <v>-15.4065192</v>
+        <v>-15.6512796</v>
       </c>
       <c r="O100">
-        <v>-1.54065192</v>
+        <v>-1.56512796</v>
       </c>
       <c r="P100">
-        <v>-13.86586728</v>
+        <v>-14.08615164</v>
       </c>
       <c r="Q100">
-        <v>-6.145867279999998</v>
+        <v>-6.366151639999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.277282479556486</v>
+        <v>4.508764959112971</v>
       </c>
       <c r="T100">
-        <v>34.5203242622675</v>
+        <v>69.040648524535</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03577009206071051</v>
+        <v>0.03540877799949121</v>
       </c>
       <c r="W100">
-        <v>0.2273654122920845</v>
+        <v>0.22745061014772</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3577009206071051</v>
+        <v>0.3540877799949121</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2702637536373725</v>
-      </c>
-      <c r="C101">
-        <v>-69.13978384747169</v>
-      </c>
-      <c r="D101">
-        <v>18.92221615252831</v>
-      </c>
-      <c r="E101">
-        <v>88.66200000000001</v>
-      </c>
-      <c r="F101">
-        <v>102.762</v>
-      </c>
-      <c r="G101">
-        <v>14.7</v>
-      </c>
-      <c r="H101">
-        <v>89.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.3</v>
-      </c>
-      <c r="K101">
-        <v>7.72</v>
-      </c>
-      <c r="L101">
-        <v>8.580000000000002</v>
-      </c>
-      <c r="M101">
-        <v>24.2312796</v>
-      </c>
-      <c r="N101">
-        <v>-15.6512796</v>
-      </c>
-      <c r="O101">
-        <v>-1.56512796</v>
-      </c>
-      <c r="P101">
-        <v>-14.08615164</v>
-      </c>
-      <c r="Q101">
-        <v>-6.366151639999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.508764959112971</v>
-      </c>
-      <c r="T101">
-        <v>69.040648524535</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03540877799949121</v>
-      </c>
-      <c r="W101">
-        <v>0.22745061014772</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3540877799949121</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
